--- a/results/genbank_table.xlsx
+++ b/results/genbank_table.xlsx
@@ -420,6 +420,30 @@
   </sheetPr>
   <dimension ref="A1:V36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="7" customWidth="1" min="17" max="17"/>
+    <col width="7" customWidth="1" min="18" max="18"/>
+    <col width="7" customWidth="1" min="19" max="19"/>
+    <col width="7" customWidth="1" min="20" max="20"/>
+    <col width="5" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3556,6 +3580,19 @@
   </sheetPr>
   <dimension ref="A1:K359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="7" customWidth="1" min="8" max="8"/>
+    <col width="7" customWidth="1" min="9" max="9"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -21061,6 +21098,11 @@
   </sheetPr>
   <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -21687,6 +21729,20 @@
   </sheetPr>
   <dimension ref="A1:L64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="8" max="8"/>
+    <col width="31" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="57" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -24421,6 +24477,10 @@
   </sheetPr>
   <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -24531,6 +24591,110 @@
   </sheetPr>
   <dimension ref="A1:CX36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="7" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="17" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="29" customWidth="1" min="17" max="17"/>
+    <col width="25" customWidth="1" min="18" max="18"/>
+    <col width="26" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="23" max="23"/>
+    <col width="20" customWidth="1" min="24" max="24"/>
+    <col width="60" customWidth="1" min="25" max="25"/>
+    <col width="21" customWidth="1" min="26" max="26"/>
+    <col width="60" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="50" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+    <col width="60" customWidth="1" min="31" max="31"/>
+    <col width="56" customWidth="1" min="32" max="32"/>
+    <col width="14" customWidth="1" min="33" max="33"/>
+    <col width="44" customWidth="1" min="34" max="34"/>
+    <col width="60" customWidth="1" min="35" max="35"/>
+    <col width="60" customWidth="1" min="36" max="36"/>
+    <col width="49" customWidth="1" min="37" max="37"/>
+    <col width="47" customWidth="1" min="38" max="38"/>
+    <col width="49" customWidth="1" min="39" max="39"/>
+    <col width="47" customWidth="1" min="40" max="40"/>
+    <col width="43" customWidth="1" min="41" max="41"/>
+    <col width="41" customWidth="1" min="42" max="42"/>
+    <col width="60" customWidth="1" min="43" max="43"/>
+    <col width="48" customWidth="1" min="44" max="44"/>
+    <col width="46" customWidth="1" min="45" max="45"/>
+    <col width="48" customWidth="1" min="46" max="46"/>
+    <col width="46" customWidth="1" min="47" max="47"/>
+    <col width="9" customWidth="1" min="48" max="48"/>
+    <col width="31" customWidth="1" min="49" max="49"/>
+    <col width="60" customWidth="1" min="50" max="50"/>
+    <col width="32" customWidth="1" min="51" max="51"/>
+    <col width="60" customWidth="1" min="52" max="52"/>
+    <col width="56" customWidth="1" min="53" max="53"/>
+    <col width="41" customWidth="1" min="54" max="54"/>
+    <col width="60" customWidth="1" min="55" max="55"/>
+    <col width="42" customWidth="1" min="56" max="56"/>
+    <col width="60" customWidth="1" min="57" max="57"/>
+    <col width="56" customWidth="1" min="58" max="58"/>
+    <col width="42" customWidth="1" min="59" max="59"/>
+    <col width="47" customWidth="1" min="60" max="60"/>
+    <col width="43" customWidth="1" min="61" max="61"/>
+    <col width="49" customWidth="1" min="62" max="62"/>
+    <col width="45" customWidth="1" min="63" max="63"/>
+    <col width="45" customWidth="1" min="64" max="64"/>
+    <col width="50" customWidth="1" min="65" max="65"/>
+    <col width="46" customWidth="1" min="66" max="66"/>
+    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="48" customWidth="1" min="68" max="68"/>
+    <col width="17" customWidth="1" min="69" max="69"/>
+    <col width="11" customWidth="1" min="70" max="70"/>
+    <col width="37" customWidth="1" min="71" max="71"/>
+    <col width="22" customWidth="1" min="72" max="72"/>
+    <col width="23" customWidth="1" min="73" max="73"/>
+    <col width="29" customWidth="1" min="74" max="74"/>
+    <col width="35" customWidth="1" min="75" max="75"/>
+    <col width="21" customWidth="1" min="76" max="76"/>
+    <col width="22" customWidth="1" min="77" max="77"/>
+    <col width="31" customWidth="1" min="78" max="78"/>
+    <col width="28" customWidth="1" min="79" max="79"/>
+    <col width="28" customWidth="1" min="80" max="80"/>
+    <col width="27" customWidth="1" min="81" max="81"/>
+    <col width="28" customWidth="1" min="82" max="82"/>
+    <col width="27" customWidth="1" min="83" max="83"/>
+    <col width="30" customWidth="1" min="84" max="84"/>
+    <col width="22" customWidth="1" min="85" max="85"/>
+    <col width="23" customWidth="1" min="86" max="86"/>
+    <col width="26" customWidth="1" min="87" max="87"/>
+    <col width="28" customWidth="1" min="88" max="88"/>
+    <col width="33" customWidth="1" min="89" max="89"/>
+    <col width="35" customWidth="1" min="90" max="90"/>
+    <col width="40" customWidth="1" min="91" max="91"/>
+    <col width="22" customWidth="1" min="92" max="92"/>
+    <col width="23" customWidth="1" min="93" max="93"/>
+    <col width="26" customWidth="1" min="94" max="94"/>
+    <col width="31" customWidth="1" min="95" max="95"/>
+    <col width="21" customWidth="1" min="96" max="96"/>
+    <col width="22" customWidth="1" min="97" max="97"/>
+    <col width="23" customWidth="1" min="98" max="98"/>
+    <col width="18" customWidth="1" min="99" max="99"/>
+    <col width="13" customWidth="1" min="100" max="100"/>
+    <col width="10" customWidth="1" min="101" max="101"/>
+    <col width="8" customWidth="1" min="102" max="102"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -25046,11 +25210,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>NC_045512.2 Severe acute respiratory syndrome coronavirus 2 isolate Wuhan-Hu-1, complete genome</t>
+          <t>MT192773.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/VNM/nCoV-19-02S/2020, complete genome</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -25088,10 +25252,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -25106,7 +25270,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -25118,16 +25282,16 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>89709</v>
+        <v>89656</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>29903</v>
+        <v>29891</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0.999598702471324</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -25137,16 +25301,32 @@
       <c r="Z2" t="b">
         <v>0</v>
       </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>C28T,C10232T</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>ORF1a:R3323C</t>
+        </is>
+      </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>C28T,C10232T</t>
+        </is>
+      </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
@@ -25154,14 +25334,18 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>ORF1a:R3323C</t>
+        </is>
+      </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
@@ -25169,10 +25353,10 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -25180,18 +25364,42 @@
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>C28T,C10232T</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>ORF1a:R3323C</t>
+        </is>
+      </c>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>C28T,C10232T</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>ORF1a:R3323C</t>
+        </is>
+      </c>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
@@ -25237,7 +25445,7 @@
         <v>24</v>
       </c>
       <c r="CB2" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -25248,7 +25456,7 @@
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="n">
@@ -25300,11 +25508,11 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MT163720.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA8-UW5/2020, complete genome</t>
+          <t>MT152824.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA2/2020, complete genome</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -25342,7 +25550,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -25360,7 +25568,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -25372,16 +25580,16 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>89164</v>
+        <v>89610</v>
       </c>
       <c r="V3" t="n">
-        <v>172</v>
+        <v>3</v>
       </c>
       <c r="W3" t="n">
-        <v>29903</v>
+        <v>29880</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9942815102163662</v>
+        <v>0.9991639634819248</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -25393,7 +25601,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>A3406C,C5784T,C8782T,C17747T,A17858G,C18060T,C23525T,T28144C</t>
+          <t>C5784T,C8782T,C17747T,A17858G,C18060T,T28144C</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr"/>
@@ -25401,39 +25609,35 @@
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>ORF1a:E1047D,ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C,ORF8:L84S,S:H655Y</t>
+          <t>ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C,ORF8:L84S</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>C23525T|21K&amp;21L&amp;22B&amp;22E&amp;23A&amp;22C&amp;24A&amp;22A&amp;23F&amp;23D&amp;20J&amp;23B&amp;22D&amp;24E&amp;22F&amp;rec&amp;25C&amp;23C&amp;24C&amp;24F&amp;23E&amp;24B&amp;23H&amp;25B&amp;25A&amp;23I&amp;24G&amp;23G&amp;24H&amp;24D&amp;21M&amp;25D&amp;24I&amp;25G&amp;25E&amp;25I&amp;25H&amp;25F</t>
-        </is>
-      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>A3406C,C5784T</t>
+          <t>C5784T</t>
         </is>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>ORF1a:E1047D,ORF1a:T1840I,S:H655Y</t>
+          <t>ORF1a:T1840I</t>
         </is>
       </c>
       <c r="AR3" t="n">
@@ -25443,10 +25647,10 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -25456,13 +25660,13 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>A3406C,C5784T,C17747T,A17858G,C18060T,C23525T</t>
+          <t>C5784T,C17747T,A17858G,C18060T</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>ORF1a:E1047D,ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C,S:H655Y</t>
+          <t>ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr"/>
@@ -25473,13 +25677,13 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>A3406C,C5784T,C23525T</t>
+          <t>C5784T</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr"/>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>ORF1a:E1047D,ORF1a:T1840I,S:H655Y</t>
+          <t>ORF1a:T1840I</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr"/>
@@ -25527,7 +25731,7 @@
         <v>24</v>
       </c>
       <c r="CB3" t="n">
-        <v>-2</v>
+        <v>-7</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
@@ -25538,7 +25742,7 @@
         </is>
       </c>
       <c r="CE3" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="n">
@@ -25590,11 +25794,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MT123290.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/IQTC01/2020, complete genome</t>
+          <t>MT192772.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/VNM/nCoV-19-01S/2020, complete genome</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -25632,13 +25836,13 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -25662,16 +25866,16 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>89636</v>
+        <v>89669</v>
       </c>
       <c r="V4" t="n">
         <v>1</v>
       </c>
       <c r="W4" t="n">
-        <v>29888</v>
+        <v>29891</v>
       </c>
       <c r="X4" t="n">
-        <v>0.999498378089155</v>
+        <v>0.999598702471324</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -25683,19 +25887,15 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+          <t>C10232T</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>0:GTT</t>
-        </is>
-      </c>
+      <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>N:P344S</t>
+          <t>ORF1a:R3323C</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
@@ -25704,7 +25904,7 @@
       <c r="AI4" t="inlineStr"/>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+          <t>C10232T</t>
         </is>
       </c>
       <c r="AK4" t="n">
@@ -25714,16 +25914,16 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>N:P344S</t>
+          <t>ORF1a:R3323C</t>
         </is>
       </c>
       <c r="AR4" t="n">
@@ -25746,13 +25946,13 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+          <t>C10232T</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>N:P344S</t>
+          <t>ORF1a:R3323C</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr"/>
@@ -25763,13 +25963,13 @@
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+          <t>C10232T</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>N:P344S</t>
+          <t>ORF1a:R3323C</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr"/>
@@ -25817,7 +26017,7 @@
         <v>24</v>
       </c>
       <c r="CB4" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -25828,7 +26028,7 @@
         </is>
       </c>
       <c r="CE4" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="n">
@@ -25880,41 +26080,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MT192765.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/PC00101P/2020, complete genome</t>
+          <t>MT163716.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA3-UW1/2020, complete genome</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>20A</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>20A</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20A</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B.1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>B.1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.694444</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -25922,7 +26122,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -25940,7 +26140,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -25952,16 +26152,16 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>89467</v>
+        <v>89657</v>
       </c>
       <c r="V5" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>29836</v>
+        <v>29903</v>
       </c>
       <c r="X5" t="n">
-        <v>0.9975253319064976</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -25973,7 +26173,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>C241T,C3037T,C14408T,C18814T,A23403G</t>
+          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G11083T,C14805T,G26144T,G29864A,T29867A,G29868A,C29870A</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -25981,7 +26181,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>ORF1b:P314L,S:D614G</t>
+          <t>ORF1a:A1049V,ORF1a:M1769I,ORF1a:L3606F,ORF3a:G251V</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -25990,7 +26190,7 @@
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>C18814T</t>
+          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G29864A,T29867A,G29868A,C29870A</t>
         </is>
       </c>
       <c r="AK5" t="n">
@@ -26000,14 +26200,18 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AN5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>ORF1a:A1049V,ORF1a:M1769I</t>
+        </is>
+      </c>
       <c r="AR5" t="n">
         <v>0</v>
       </c>
@@ -26015,37 +26219,45 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>NODE_0000764</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>C18814T</t>
+          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G11083T,C14805T,G26144T,G29864A,T29867A,G29868A,C29870A</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>ORF1a:A1049V,ORF1a:M1769I,ORF1a:L3606F,ORF3a:G251V</t>
+        </is>
+      </c>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>NODE_0000764</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>C18814T</t>
+          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G11083T,C14805T,G26144T,G29864A,T29867A,G29868A,C29870A</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>ORF1a:A1049V,ORF1a:M1769I,ORF1a:L3606F,ORF3a:G251V</t>
+        </is>
+      </c>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
@@ -26091,10 +26303,10 @@
         <v>24</v>
       </c>
       <c r="CB5" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>8.333333</v>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
@@ -26102,7 +26314,7 @@
         </is>
       </c>
       <c r="CE5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="n">
@@ -26154,37 +26366,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MT152824.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA2/2020, complete genome</t>
+          <t>MT192759.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/TWN/CGMH-CGU-01/2020, complete genome</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -26196,7 +26408,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -26214,7 +26426,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -26226,16 +26438,16 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>89610</v>
+        <v>89586</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="W6" t="n">
-        <v>29880</v>
+        <v>29889</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9991639634819248</v>
+        <v>0.9986289001103568</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -26245,28 +26457,16 @@
       <c r="Z6" t="b">
         <v>0</v>
       </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>C5784T,C8782T,C17747T,A17858G,C18060T,T28144C</t>
-        </is>
-      </c>
+      <c r="AA6" t="inlineStr"/>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C,ORF8:L84S</t>
-        </is>
-      </c>
+      <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>C5784T</t>
-        </is>
-      </c>
+      <c r="AJ6" t="inlineStr"/>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
@@ -26274,18 +26474,14 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>ORF1a:T1840I</t>
-        </is>
-      </c>
+      <c r="AQ6" t="inlineStr"/>
       <c r="AR6" t="n">
         <v>0</v>
       </c>
@@ -26293,45 +26489,29 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>internal_b384</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>C5784T,C17747T,A17858G,C18060T</t>
-        </is>
-      </c>
+          <t>NODE_0000000</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr"/>
       <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C</t>
-        </is>
-      </c>
+      <c r="AZ6" t="inlineStr"/>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>A.1</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>C5784T</t>
-        </is>
-      </c>
+          <t>NODE_0000000</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr"/>
       <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>ORF1a:T1840I</t>
-        </is>
-      </c>
+      <c r="BE6" t="inlineStr"/>
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
@@ -26377,7 +26557,7 @@
         <v>24</v>
       </c>
       <c r="CB6" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="CC6" t="n">
         <v>0</v>
@@ -26388,7 +26568,7 @@
         </is>
       </c>
       <c r="CE6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="n">
@@ -26440,11 +26620,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MT192759.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/TWN/CGMH-CGU-01/2020, complete genome</t>
+          <t>MT184908.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/Cruise-CDC-3054886-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -26482,7 +26662,7 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -26500,7 +26680,7 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -26512,16 +26692,16 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>89586</v>
+        <v>89630</v>
       </c>
       <c r="V7" t="n">
-        <v>28</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>29889</v>
+        <v>29882</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9986289001103568</v>
+        <v>0.9992977293248168</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -26531,16 +26711,28 @@
       <c r="Z7" t="b">
         <v>0</v>
       </c>
-      <c r="AA7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>C254T,G11083T,G29736T,G29751C</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F</t>
+        </is>
+      </c>
       <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>C254T,G29736T,G29751C</t>
+        </is>
+      </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
@@ -26548,10 +26740,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
@@ -26574,18 +26766,34 @@
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>C254T,G11083T,G29736T,G29751C</t>
+        </is>
+      </c>
       <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F</t>
+        </is>
+      </c>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>C254T,G11083T,G29736T,G29751C</t>
+        </is>
+      </c>
       <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F</t>
+        </is>
+      </c>
       <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
@@ -26631,7 +26839,7 @@
         <v>24</v>
       </c>
       <c r="CB7" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="CC7" t="n">
         <v>0</v>
@@ -26642,7 +26850,7 @@
         </is>
       </c>
       <c r="CE7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CF7" t="inlineStr"/>
       <c r="CG7" t="n">
@@ -26694,37 +26902,37 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MT135044.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/235/2020, complete genome</t>
+          <t>NC_045512.2 Severe acute respiratory syndrome coronavirus 2 isolate Wuhan-Hu-1, complete genome</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -26736,7 +26944,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -26754,7 +26962,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -26766,7 +26974,7 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>89693</v>
+        <v>89709</v>
       </c>
       <c r="V8" t="n">
         <v>1</v>
@@ -26785,28 +26993,16 @@
       <c r="Z8" t="b">
         <v>0</v>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>T4402C,G5062T,C8782T,T28144C</t>
-        </is>
-      </c>
+      <c r="AA8" t="inlineStr"/>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>ORF1a:L1599F,ORF8:L84S</t>
-        </is>
-      </c>
+      <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>T4402C,G5062T</t>
-        </is>
-      </c>
+      <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
@@ -26814,18 +27010,14 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>ORF1a:L1599F</t>
-        </is>
-      </c>
+      <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="n">
         <v>0</v>
       </c>
@@ -26833,45 +27025,29 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>internal_b384</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>T4402C,G5062T</t>
-        </is>
-      </c>
+          <t>NODE_0000000</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr"/>
       <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>ORF1a:L1599F</t>
-        </is>
-      </c>
+      <c r="AZ8" t="inlineStr"/>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>internal_b384</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>T4402C,G5062T</t>
-        </is>
-      </c>
+          <t>NODE_0000000</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr"/>
       <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>ORF1a:L1599F</t>
-        </is>
-      </c>
+      <c r="BE8" t="inlineStr"/>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
@@ -26917,7 +27093,7 @@
         <v>24</v>
       </c>
       <c r="CB8" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="CC8" t="n">
         <v>0</v>
@@ -26928,7 +27104,7 @@
         </is>
       </c>
       <c r="CE8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="n">
@@ -26980,37 +27156,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MT159718.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/Cruise-CDC-03053369-001/2020, complete genome</t>
+          <t>MT135044.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/235/2020, complete genome</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -27022,7 +27198,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -27052,16 +27228,16 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>89634</v>
+        <v>89693</v>
       </c>
       <c r="V9" t="n">
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>29882</v>
+        <v>29903</v>
       </c>
       <c r="X9" t="n">
-        <v>0.9992977293248168</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -27073,7 +27249,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>G11083T,C28409T,G29736T</t>
+          <t>T4402C,G5062T,C8782T,T28144C</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -27081,7 +27257,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>N:P46S,ORF1a:L3606F</t>
+          <t>ORF1a:L1599F,ORF8:L84S</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -27090,7 +27266,7 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>C28409T,G29736T</t>
+          <t>T4402C,G5062T</t>
         </is>
       </c>
       <c r="AK9" t="n">
@@ -27109,7 +27285,7 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>N:P46S</t>
+          <t>ORF1a:L1599F</t>
         </is>
       </c>
       <c r="AR9" t="n">
@@ -27127,35 +27303,35 @@
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>G11083T,C28409T,G29736T</t>
+          <t>T4402C,G5062T</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>N:P46S,ORF1a:L3606F</t>
+          <t>ORF1a:L1599F</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>G11083T,C28409T,G29736T</t>
+          <t>T4402C,G5062T</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>N:P46S,ORF1a:L3606F</t>
+          <t>ORF1a:L1599F</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr"/>
@@ -27266,11 +27442,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MT163716.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA3-UW1/2020, complete genome</t>
+          <t>MT126808.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/BRA/SP02/2020, complete genome</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -27300,7 +27476,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.694444</v>
+        <v>0</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -27308,7 +27484,7 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -27326,7 +27502,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -27338,16 +27514,16 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>89657</v>
+        <v>89612</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>29903</v>
+        <v>29876</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0.9990970805604787</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -27359,7 +27535,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G11083T,C14805T,G26144T,G29864A,T29867A,G29868A,C29870A</t>
+          <t>G11083T,C14805T,T17247C,G26144T</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -27367,7 +27543,7 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>ORF1a:A1049V,ORF1a:M1769I,ORF1a:L3606F,ORF3a:G251V</t>
+          <t>ORF1a:L3606F,ORF3a:G251V</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -27376,7 +27552,7 @@
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G29864A,T29867A,G29868A,C29870A</t>
+          <t>T17247C</t>
         </is>
       </c>
       <c r="AK10" t="n">
@@ -27386,18 +27562,14 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>ORF1a:A1049V,ORF1a:M1769I</t>
-        </is>
-      </c>
+      <c r="AQ10" t="inlineStr"/>
       <c r="AR10" t="n">
         <v>0</v>
       </c>
@@ -27405,10 +27577,10 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -27418,13 +27590,13 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G11083T,C14805T,G26144T,G29864A,T29867A,G29868A,C29870A</t>
+          <t>G11083T,C14805T,T17247C,G26144T</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>ORF1a:A1049V,ORF1a:M1769I,ORF1a:L3606F,ORF3a:G251V</t>
+          <t>ORF1a:L3606F,ORF3a:G251V</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr"/>
@@ -27435,13 +27607,13 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G11083T,C14805T,G26144T,G29864A,T29867A,G29868A,C29870A</t>
+          <t>G11083T,C14805T,T17247C,G26144T</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>ORF1a:A1049V,ORF1a:M1769I,ORF1a:L3606F,ORF3a:G251V</t>
+          <t>ORF1a:L3606F,ORF3a:G251V</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr"/>
@@ -27489,10 +27661,10 @@
         <v>24</v>
       </c>
       <c r="CB10" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="CC10" t="n">
-        <v>8.333333</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
@@ -27500,7 +27672,7 @@
         </is>
       </c>
       <c r="CE10" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="n">
@@ -27838,37 +28010,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MT192773.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/VNM/nCoV-19-02S/2020, complete genome</t>
+          <t>MT192765.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/PC00101P/2020, complete genome</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>20A</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>20A</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>20A</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B.1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B.1</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -27880,26 +28052,26 @@
         </is>
       </c>
       <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>2</v>
       </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -27910,16 +28082,16 @@
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>89656</v>
+        <v>89467</v>
       </c>
       <c r="V12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W12" t="n">
-        <v>29891</v>
+        <v>29836</v>
       </c>
       <c r="X12" t="n">
-        <v>0.999598702471324</v>
+        <v>0.9975253319064976</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -27931,19 +28103,15 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>C28T,C10232T</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+          <t>C241T,C3037T,C14408T,C18814T,A23403G</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>ORF1a:R3323C</t>
+          <t>ORF1b:P314L,S:D614G</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
@@ -27952,7 +28120,7 @@
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>C28T,C10232T</t>
+          <t>C18814T</t>
         </is>
       </c>
       <c r="AK12" t="n">
@@ -27962,18 +28130,14 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>ORF1a:R3323C</t>
-        </is>
-      </c>
+      <c r="AQ12" t="inlineStr"/>
       <c r="AR12" t="n">
         <v>0</v>
       </c>
@@ -27981,53 +28145,37 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>NODE_0000764</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>C28T,C10232T</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>ORF1a:R3323C</t>
-        </is>
-      </c>
+          <t>C18814T</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>NODE_0000764</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>C28T,C10232T</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>ORF1a:R3323C</t>
-        </is>
-      </c>
+          <t>C18814T</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
       <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
@@ -28073,7 +28221,7 @@
         <v>24</v>
       </c>
       <c r="CB12" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -28084,7 +28232,7 @@
         </is>
       </c>
       <c r="CE12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CF12" t="inlineStr"/>
       <c r="CG12" t="n">
@@ -28136,11 +28284,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MT126808.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/BRA/SP02/2020, complete genome</t>
+          <t>MT159718.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/Cruise-CDC-03053369-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -28178,7 +28326,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -28208,16 +28356,16 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>89612</v>
+        <v>89634</v>
       </c>
       <c r="V13" t="n">
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>29876</v>
+        <v>29882</v>
       </c>
       <c r="X13" t="n">
-        <v>0.9990970805604787</v>
+        <v>0.9992977293248168</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -28229,7 +28377,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>G11083T,C14805T,T17247C,G26144T</t>
+          <t>G11083T,C28409T,G29736T</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr"/>
@@ -28237,7 +28385,7 @@
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,ORF3a:G251V</t>
+          <t>N:P46S,ORF1a:L3606F</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr"/>
@@ -28246,7 +28394,7 @@
       <c r="AI13" t="inlineStr"/>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>T17247C</t>
+          <t>C28409T,G29736T</t>
         </is>
       </c>
       <c r="AK13" t="n">
@@ -28256,14 +28404,18 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>N:P46S</t>
+        </is>
+      </c>
       <c r="AR13" t="n">
         <v>0</v>
       </c>
@@ -28271,10 +28423,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -28284,13 +28436,13 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>G11083T,C14805T,T17247C,G26144T</t>
+          <t>G11083T,C28409T,G29736T</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,ORF3a:G251V</t>
+          <t>N:P46S,ORF1a:L3606F</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr"/>
@@ -28301,13 +28453,13 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>G11083T,C14805T,T17247C,G26144T</t>
+          <t>G11083T,C28409T,G29736T</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr"/>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,ORF3a:G251V</t>
+          <t>N:P46S,ORF1a:L3606F</t>
         </is>
       </c>
       <c r="BF13" t="inlineStr"/>
@@ -28355,7 +28507,7 @@
         <v>24</v>
       </c>
       <c r="CB13" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
@@ -28366,7 +28518,7 @@
         </is>
       </c>
       <c r="CE13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="CF13" t="inlineStr"/>
       <c r="CG13" t="n">
@@ -28418,37 +28570,37 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MT184908.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/Cruise-CDC-3054886-001/2020, complete genome</t>
+          <t>MT163720.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA8-UW5/2020, complete genome</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -28460,7 +28612,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -28478,7 +28630,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -28490,16 +28642,16 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>89630</v>
+        <v>89164</v>
       </c>
       <c r="V14" t="n">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="W14" t="n">
-        <v>29882</v>
+        <v>29903</v>
       </c>
       <c r="X14" t="n">
-        <v>0.9992977293248168</v>
+        <v>0.9942815102163662</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -28511,7 +28663,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>C254T,G11083T,G29736T,G29751C</t>
+          <t>A3406C,C5784T,C8782T,C17747T,A17858G,C18060T,C23525T,T28144C</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
@@ -28519,33 +28671,41 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F</t>
+          <t>ORF1a:E1047D,ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C,ORF8:L84S,S:H655Y</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>C23525T|21K&amp;21L&amp;22B&amp;22E&amp;23A&amp;22C&amp;24A&amp;22A&amp;23F&amp;23D&amp;20J&amp;23B&amp;22D&amp;24E&amp;22F&amp;rec&amp;25C&amp;23C&amp;24C&amp;24F&amp;23E&amp;24B&amp;23H&amp;25B&amp;25A&amp;23I&amp;24G&amp;23G&amp;24H&amp;24D&amp;21M&amp;25D&amp;24I&amp;25G&amp;25E&amp;25I&amp;25H&amp;25F</t>
+        </is>
+      </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>C254T,G29736T,G29751C</t>
+          <t>A3406C,C5784T</t>
         </is>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN14" t="n">
         <v>3</v>
       </c>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>ORF1a:E1047D,ORF1a:T1840I,S:H655Y</t>
+        </is>
+      </c>
       <c r="AR14" t="n">
         <v>0</v>
       </c>
@@ -28553,43 +28713,43 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>C254T,G11083T,G29736T,G29751C</t>
+          <t>A3406C,C5784T,C17747T,A17858G,C18060T,C23525T</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F</t>
+          <t>ORF1a:E1047D,ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C,S:H655Y</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>C254T,G11083T,G29736T,G29751C</t>
+          <t>A3406C,C5784T,C23525T</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr"/>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F</t>
+          <t>ORF1a:E1047D,ORF1a:T1840I,S:H655Y</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr"/>
@@ -28637,7 +28797,7 @@
         <v>24</v>
       </c>
       <c r="CB14" t="n">
-        <v>-5</v>
+        <v>-2</v>
       </c>
       <c r="CC14" t="n">
         <v>0</v>
@@ -28648,7 +28808,7 @@
         </is>
       </c>
       <c r="CE14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="CF14" t="inlineStr"/>
       <c r="CG14" t="n">
@@ -28700,11 +28860,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MT159716.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/Cruise-CDC-03056442-001/2020, complete genome</t>
+          <t>MT123290.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/IQTC01/2020, complete genome</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -28742,13 +28902,13 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L15" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -28760,10 +28920,10 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -28772,16 +28932,16 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>89586</v>
+        <v>89636</v>
       </c>
       <c r="V15" t="n">
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>29882</v>
+        <v>29888</v>
       </c>
       <c r="X15" t="n">
-        <v>0.9992977293248168</v>
+        <v>0.999498378089155</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -28793,51 +28953,47 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>G11083T,C22033A</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>509-523</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr"/>
+          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0:GTT</t>
+        </is>
+      </c>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,S:F157L</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>ORF1a:G82-,ORF1a:H83-,ORF1a:V84-,ORF1a:M85-,ORF1a:V86-</t>
-        </is>
-      </c>
+          <t>N:P344S</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="inlineStr"/>
       <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>C22033A|24A&amp;24E&amp;22D&amp;25C&amp;24C&amp;23C&amp;24F&amp;23F&amp;24B&amp;rec&amp;25B&amp;25A&amp;24G&amp;23I&amp;24H&amp;24D&amp;25D&amp;25G&amp;24I&amp;25E&amp;25H&amp;25F</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+        </is>
+      </c>
       <c r="AK15" t="n">
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AN15" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>S:F157L</t>
+          <t>N:P344S</t>
         </is>
       </c>
       <c r="AR15" t="n">
@@ -28860,24 +29016,16 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>G11083T,C22033A</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>509-523</t>
-        </is>
-      </c>
+          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,S:F157L</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>ORF1a:G82-,ORF1a:H83-,ORF1a:V84-,ORF1a:M85-,ORF1a:V86-</t>
-        </is>
-      </c>
+          <t>N:P344S</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr"/>
       <c r="BB15" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
@@ -28885,24 +29033,16 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>G11083T,C22033A</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>509-523</t>
-        </is>
-      </c>
+          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr"/>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,S:F157L</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>ORF1a:G82-,ORF1a:H83-,ORF1a:V84-,ORF1a:M85-,ORF1a:V86-</t>
-        </is>
-      </c>
+          <t>N:P344S</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr"/>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr"/>
@@ -28947,7 +29087,7 @@
         <v>24</v>
       </c>
       <c r="CB15" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="CC15" t="n">
         <v>0</v>
@@ -28958,7 +29098,7 @@
         </is>
       </c>
       <c r="CE15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CF15" t="inlineStr"/>
       <c r="CG15" t="n">
@@ -29010,41 +29150,41 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MT192772.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/VNM/nCoV-19-01S/2020, complete genome</t>
+          <t>MT188341.1 Severe acute respiratory syndrome coronavirus 2 isolate USA/MN1-MDH1/2020, complete genome</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.694444</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -29052,13 +29192,13 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -29070,28 +29210,28 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>89669</v>
+        <v>89403</v>
       </c>
       <c r="V16" t="n">
-        <v>1</v>
+        <v>55</v>
       </c>
       <c r="W16" t="n">
-        <v>29891</v>
+        <v>29903</v>
       </c>
       <c r="X16" t="n">
-        <v>0.999598702471324</v>
+        <v>0.9981941611209576</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -29103,24 +29243,36 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>C10232T</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr"/>
-      <c r="AC16" t="inlineStr"/>
+          <t>A6035G,C8782T,A16467G,C17747T,A17858G,C18060T,C21386T,C23185T,T28144C,T29867C,C29870A,A29893G,A29897G,A29898G</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>29837-29859</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>21384:TTC,29866:CCTCT,29903:A</t>
+        </is>
+      </c>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>ORF1a:R3323C</t>
+          <t>ORF1a:S1924G,ORF1b:P1427L,ORF1b:Y1464C,ORF1b:S2640F,ORF8:L84S</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>ORF1b:2639:F</t>
+        </is>
+      </c>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>C10232T</t>
+          <t>A6035G,A16467G,C21386T,C23185T,T29867C,C29870A,A29893G,A29897G,A29898G</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -29130,16 +29282,16 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AN16" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>ORF1a:R3323C</t>
+          <t>ORF1a:S1924G,ORF1b:S2640F</t>
         </is>
       </c>
       <c r="AR16" t="n">
@@ -29149,43 +29301,51 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>C10232T</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>A6035G,A16467G,C17747T,A17858G,C18060T,C21386T,C23185T,T29867C,C29870A,A29893G,A29897G,A29898G</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>29837-29859</t>
+        </is>
+      </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>ORF1a:R3323C</t>
+          <t>ORF1a:S1924G,ORF1b:P1427L,ORF1b:Y1464C,ORF1b:S2640F</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>C10232T</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr"/>
+          <t>A6035G,A16467G,C21386T,C23185T,T29867C,C29870A,A29893G,A29897G,A29898G</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>29837-29859</t>
+        </is>
+      </c>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>ORF1a:R3323C</t>
+          <t>ORF1a:S1924G,ORF1b:S2640F</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr"/>
@@ -29233,10 +29393,10 @@
         <v>24</v>
       </c>
       <c r="CB16" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="CC16" t="n">
-        <v>0</v>
+        <v>8.333333</v>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
@@ -29244,7 +29404,7 @@
         </is>
       </c>
       <c r="CE16" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="CF16" t="inlineStr"/>
       <c r="CG16" t="n">
@@ -29296,41 +29456,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MT188341.1 Severe acute respiratory syndrome coronavirus 2 isolate USA/MN1-MDH1/2020, complete genome</t>
+          <t>MT159716.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/Cruise-CDC-03056442-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.694444</v>
+        <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -29338,13 +29498,13 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -29356,28 +29516,28 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
+        <v>2</v>
+      </c>
+      <c r="R17" t="n">
         <v>5</v>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>89403</v>
+        <v>89586</v>
       </c>
       <c r="V17" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>29903</v>
+        <v>29882</v>
       </c>
       <c r="X17" t="n">
-        <v>0.9981941611209576</v>
+        <v>0.9992977293248168</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -29389,55 +29549,51 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>A6035G,C8782T,A16467G,C17747T,A17858G,C18060T,C21386T,C23185T,T28144C,T29867C,C29870A,A29893G,A29897G,A29898G</t>
+          <t>G11083T,C22033A</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>29837-29859</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>21384:TTC,29866:CCTCT,29903:A</t>
-        </is>
-      </c>
+          <t>509-523</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>ORF1a:S1924G,ORF1b:P1427L,ORF1b:Y1464C,ORF1b:S2640F,ORF8:L84S</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>ORF1b:2639:F</t>
-        </is>
-      </c>
+          <t>ORF1a:L3606F,S:F157L</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>ORF1a:G82-,ORF1a:H83-,ORF1a:V84-,ORF1a:M85-,ORF1a:V86-</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>A6035G,A16467G,C21386T,C23185T,T29867C,C29870A,A29893G,A29897G,A29898G</t>
-        </is>
-      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>C22033A|24A&amp;24E&amp;22D&amp;25C&amp;24C&amp;23C&amp;24F&amp;23F&amp;24B&amp;rec&amp;25B&amp;25A&amp;24G&amp;23I&amp;24H&amp;24D&amp;25D&amp;25G&amp;24I&amp;25E&amp;25H&amp;25F</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr"/>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM17" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>ORF1a:S1924G,ORF1b:S2640F</t>
+          <t>S:F157L</t>
         </is>
       </c>
       <c r="AR17" t="n">
@@ -29447,54 +29603,62 @@
         <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>A6035G,A16467G,C17747T,A17858G,C18060T,C21386T,C23185T,T29867C,C29870A,A29893G,A29897G,A29898G</t>
+          <t>G11083T,C22033A</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>29837-29859</t>
+          <t>509-523</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>ORF1a:S1924G,ORF1b:P1427L,ORF1b:Y1464C,ORF1b:S2640F</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
+          <t>ORF1a:L3606F,S:F157L</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>ORF1a:G82-,ORF1a:H83-,ORF1a:V84-,ORF1a:M85-,ORF1a:V86-</t>
+        </is>
+      </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>A6035G,A16467G,C21386T,C23185T,T29867C,C29870A,A29893G,A29897G,A29898G</t>
+          <t>G11083T,C22033A</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>29837-29859</t>
+          <t>509-523</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>ORF1a:S1924G,ORF1b:S2640F</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr"/>
+          <t>ORF1a:L3606F,S:F157L</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>ORF1a:G82-,ORF1a:H83-,ORF1a:V84-,ORF1a:M85-,ORF1a:V86-</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr"/>
@@ -29539,10 +29703,10 @@
         <v>24</v>
       </c>
       <c r="CB17" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="CC17" t="n">
-        <v>8.333333</v>
+        <v>0</v>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
@@ -29550,7 +29714,7 @@
         </is>
       </c>
       <c r="CE17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="CF17" t="inlineStr"/>
       <c r="CG17" t="n">
@@ -29896,11 +30060,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MT072688.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/NPL/61-TW/2020, complete genome</t>
+          <t>MT093631.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/WH-09/2020, complete genome</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -29968,16 +30132,16 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>89429</v>
+        <v>89576</v>
       </c>
       <c r="V19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="W19" t="n">
-        <v>29826</v>
+        <v>29873</v>
       </c>
       <c r="X19" t="n">
-        <v>0.9969233856134836</v>
+        <v>0.9985620171889108</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -29989,7 +30153,7 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>C24034T</t>
+          <t>C186T</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
@@ -30002,7 +30166,7 @@
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>C24034T</t>
+          <t>C186T</t>
         </is>
       </c>
       <c r="AK19" t="n">
@@ -30040,7 +30204,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>C24034T</t>
+          <t>C186T</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -30053,7 +30217,7 @@
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>C24034T</t>
+          <t>C186T</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr"/>
@@ -30166,11 +30330,11 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MT039873.1 Severe acute respiratory syndrome coronavirus 2 isolate HZ-1, complete genome</t>
+          <t>MT093571.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/SWE/01/2020, complete genome</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -30208,7 +30372,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -30226,7 +30390,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -30238,16 +30402,16 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>89499</v>
+        <v>89630</v>
       </c>
       <c r="V20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>29836</v>
+        <v>29886</v>
       </c>
       <c r="X20" t="n">
-        <v>0.9976590977493895</v>
+        <v>0.9994314951677088</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -30257,16 +30421,28 @@
       <c r="Z20" t="b">
         <v>0</v>
       </c>
-      <c r="AA20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
+        </is>
+      </c>
       <c r="AB20" t="inlineStr"/>
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
+        </is>
+      </c>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
+        </is>
+      </c>
       <c r="AK20" t="n">
         <v>0</v>
       </c>
@@ -30274,14 +30450,18 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
+        </is>
+      </c>
       <c r="AR20" t="n">
         <v>0</v>
       </c>
@@ -30289,10 +30469,10 @@
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -30300,18 +30480,34 @@
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
+        </is>
+      </c>
       <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
+        </is>
+      </c>
       <c r="BA20" t="inlineStr"/>
       <c r="BB20" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="BC20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
+        </is>
+      </c>
       <c r="BD20" t="inlineStr"/>
-      <c r="BE20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
+        </is>
+      </c>
       <c r="BF20" t="inlineStr"/>
       <c r="BG20" t="inlineStr"/>
       <c r="BH20" t="inlineStr"/>
@@ -30357,7 +30553,7 @@
         <v>24</v>
       </c>
       <c r="CB20" t="n">
-        <v>-8</v>
+        <v>-1</v>
       </c>
       <c r="CC20" t="n">
         <v>0</v>
@@ -30368,7 +30564,7 @@
         </is>
       </c>
       <c r="CE20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="CF20" t="inlineStr"/>
       <c r="CG20" t="n">
@@ -30420,11 +30616,11 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MT066156.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/ITA/INMI1/2020, complete genome</t>
+          <t>MT072688.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/NPL/61-TW/2020, complete genome</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -30462,7 +30658,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -30474,13 +30670,13 @@
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -30489,23 +30685,23 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>89592</v>
+        <v>89429</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="W21" t="n">
-        <v>29867</v>
+        <v>29826</v>
       </c>
       <c r="X21" t="n">
-        <v>0.9987626659532488</v>
+        <v>0.9969233856134836</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>E:1,M:1,N:1,ORF1a:0.9997727789138832,ORF1b:1,ORF3a:1,ORF6:1,ORF7a:1,ORF7b:1,ORF8:1,ORF9b:1,S:1</t>
+          <t>E:1,M:1,N:1,ORF1a:1,ORF1b:1,ORF3a:1,ORF6:1,ORF7a:1,ORF7b:1,ORF8:1,ORF9b:1,S:1</t>
         </is>
       </c>
       <c r="Z21" t="b">
@@ -30513,32 +30709,24 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>A2269T,G26144T</t>
+          <t>C24034T</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>ORF3a:G251V</t>
-        </is>
-      </c>
+      <c r="AE21" t="inlineStr"/>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>T14805C</t>
-        </is>
-      </c>
+      <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>A2269T</t>
+          <t>C24034T</t>
         </is>
       </c>
       <c r="AK21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
@@ -30547,7 +30735,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
@@ -30564,9 +30752,7 @@
       <c r="AU21" t="n">
         <v>0</v>
       </c>
-      <c r="AV21" t="n">
-        <v>11083</v>
-      </c>
+      <c r="AV21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
@@ -30574,15 +30760,11 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>A2269T,G26144T</t>
+          <t>C24034T</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>ORF3a:G251V</t>
-        </is>
-      </c>
+      <c r="AZ21" t="inlineStr"/>
       <c r="BA21" t="inlineStr"/>
       <c r="BB21" t="inlineStr">
         <is>
@@ -30591,15 +30773,11 @@
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>A2269T,G26144T</t>
+          <t>C24034T</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>ORF3a:G251V</t>
-        </is>
-      </c>
+      <c r="BE21" t="inlineStr"/>
       <c r="BF21" t="inlineStr"/>
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="inlineStr"/>
@@ -30611,11 +30789,7 @@
       <c r="BN21" t="inlineStr"/>
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr"/>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>ORF1a:3606</t>
-        </is>
-      </c>
+      <c r="BQ21" t="inlineStr"/>
       <c r="BR21" t="inlineStr"/>
       <c r="BS21" t="n">
         <v>3000</v>
@@ -30629,7 +30803,7 @@
         </is>
       </c>
       <c r="BV21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW21" t="n">
         <v>10</v>
@@ -30649,7 +30823,7 @@
         <v>24</v>
       </c>
       <c r="CB21" t="n">
-        <v>-1</v>
+        <v>-7</v>
       </c>
       <c r="CC21" t="n">
         <v>0</v>
@@ -30660,7 +30834,7 @@
         </is>
       </c>
       <c r="CE21" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="CF21" t="inlineStr"/>
       <c r="CG21" t="n">
@@ -30712,37 +30886,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MT093571.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/SWE/01/2020, complete genome</t>
+          <t>MT066175.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/NTU01/TWN/human/2020, complete genome</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -30754,7 +30928,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -30772,7 +30946,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -30784,16 +30958,16 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>89630</v>
+        <v>89602</v>
       </c>
       <c r="V22" t="n">
         <v>1</v>
       </c>
       <c r="W22" t="n">
-        <v>29886</v>
+        <v>29870</v>
       </c>
       <c r="X22" t="n">
-        <v>0.9994314951677088</v>
+        <v>0.9988964317961408</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -30805,7 +30979,7 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
+          <t>C8782T,T28144C</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
@@ -30813,18 +30987,14 @@
       <c r="AD22" t="inlineStr"/>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
+          <t>ORF8:L84S</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
-        </is>
-      </c>
+      <c r="AJ22" t="inlineStr"/>
       <c r="AK22" t="n">
         <v>0</v>
       </c>
@@ -30832,18 +31002,14 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
-        </is>
-      </c>
+      <c r="AQ22" t="inlineStr"/>
       <c r="AR22" t="n">
         <v>0</v>
       </c>
@@ -30851,45 +31017,29 @@
         <v>0</v>
       </c>
       <c r="AT22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
-        </is>
-      </c>
+          <t>internal_b384</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr"/>
       <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
-        </is>
-      </c>
+      <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="inlineStr"/>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
-        </is>
-      </c>
+          <t>internal_b384</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr"/>
       <c r="BD22" t="inlineStr"/>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
-        </is>
-      </c>
+      <c r="BE22" t="inlineStr"/>
       <c r="BF22" t="inlineStr"/>
       <c r="BG22" t="inlineStr"/>
       <c r="BH22" t="inlineStr"/>
@@ -30935,7 +31085,7 @@
         <v>24</v>
       </c>
       <c r="CB22" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="CC22" t="n">
         <v>0</v>
@@ -30946,7 +31096,7 @@
         </is>
       </c>
       <c r="CE22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CF22" t="inlineStr"/>
       <c r="CG22" t="n">
@@ -30998,11 +31148,11 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MT066175.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/NTU01/TWN/human/2020, complete genome</t>
+          <t>MN997409.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/AZ-CDC-02993465-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -31040,26 +31190,26 @@
         </is>
       </c>
       <c r="K23" t="n">
+        <v>4</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
         <v>2</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>1</v>
-      </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
@@ -31070,16 +31220,16 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>89602</v>
+        <v>89630</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>29870</v>
+        <v>29882</v>
       </c>
       <c r="X23" t="n">
-        <v>0.9988964317961408</v>
+        <v>0.9992977293248168</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -31091,7 +31241,7 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>C8782T,T28144C</t>
+          <t>C8782T,G11083T,T28144C,C29095T</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -31099,14 +31249,18 @@
       <c r="AD23" t="inlineStr"/>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>ORF8:L84S</t>
+          <t>ORF1a:L3606F,ORF8:L84S</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>G11083T,C29095T</t>
+        </is>
+      </c>
       <c r="AK23" t="n">
         <v>0</v>
       </c>
@@ -31114,14 +31268,18 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F</t>
+        </is>
+      </c>
       <c r="AR23" t="n">
         <v>0</v>
       </c>
@@ -31129,10 +31287,10 @@
         <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -31140,18 +31298,34 @@
           <t>internal_b384</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr"/>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>G11083T,C29095T</t>
+        </is>
+      </c>
       <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F</t>
+        </is>
+      </c>
       <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="inlineStr">
         <is>
           <t>internal_b384</t>
         </is>
       </c>
-      <c r="BC23" t="inlineStr"/>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>G11083T,C29095T</t>
+        </is>
+      </c>
       <c r="BD23" t="inlineStr"/>
-      <c r="BE23" t="inlineStr"/>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F</t>
+        </is>
+      </c>
       <c r="BF23" t="inlineStr"/>
       <c r="BG23" t="inlineStr"/>
       <c r="BH23" t="inlineStr"/>
@@ -31197,7 +31371,7 @@
         <v>24</v>
       </c>
       <c r="CB23" t="n">
-        <v>-8</v>
+        <v>-6</v>
       </c>
       <c r="CC23" t="n">
         <v>0</v>
@@ -31208,7 +31382,7 @@
         </is>
       </c>
       <c r="CE23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CF23" t="inlineStr"/>
       <c r="CG23" t="n">
@@ -31260,37 +31434,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MT020781.2 Severe acute respiratory syndrome coronavirus 2 isolate nCoV-FIN-29-Jan-2020, complete genome</t>
+          <t>MT050493.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/IND/166/2020, complete genome</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -31302,7 +31476,7 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -31320,7 +31494,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -31332,16 +31506,16 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>89410</v>
+        <v>89529</v>
       </c>
       <c r="V24" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="W24" t="n">
-        <v>29806</v>
+        <v>29871</v>
       </c>
       <c r="X24" t="n">
-        <v>0.9967561783098686</v>
+        <v>0.9982610440424038</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -31353,7 +31527,7 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>A1C,C21707T</t>
+          <t>A1691G,C6501T,C8782T,C16877T,C24351T,T28144C</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -31361,7 +31535,7 @@
       <c r="AD24" t="inlineStr"/>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>S:H49Y</t>
+          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,ORF8:L84S,S:A930V</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr"/>
@@ -31370,7 +31544,7 @@
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>A1C,C21707T</t>
+          <t>A1691G,C6501T,C16877T,C24351T</t>
         </is>
       </c>
       <c r="AK24" t="n">
@@ -31380,16 +31554,16 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AN24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>S:H49Y</t>
+          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,S:A930V</t>
         </is>
       </c>
       <c r="AR24" t="n">
@@ -31399,43 +31573,43 @@
         <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>A1C,C21707T</t>
+          <t>A1691G,C6501T,C16877T,C24351T</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>S:H49Y</t>
+          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,S:A930V</t>
         </is>
       </c>
       <c r="BA24" t="inlineStr"/>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>A1C,C21707T</t>
+          <t>A1691G,C6501T,C16877T,C24351T</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr"/>
       <c r="BE24" t="inlineStr">
         <is>
-          <t>S:H49Y</t>
+          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,S:A930V</t>
         </is>
       </c>
       <c r="BF24" t="inlineStr"/>
@@ -31483,7 +31657,7 @@
         <v>24</v>
       </c>
       <c r="CB24" t="n">
-        <v>-6</v>
+        <v>-4</v>
       </c>
       <c r="CC24" t="n">
         <v>0</v>
@@ -31494,7 +31668,7 @@
         </is>
       </c>
       <c r="CE24" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="CF24" t="inlineStr"/>
       <c r="CG24" t="n">
@@ -31546,37 +31720,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MT093631.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/WH-09/2020, complete genome</t>
+          <t>MT049951.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/Yunnan-01/2020, complete genome</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -31588,7 +31762,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -31606,7 +31780,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -31618,16 +31792,16 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>89576</v>
+        <v>89689</v>
       </c>
       <c r="V25" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>29873</v>
+        <v>29903</v>
       </c>
       <c r="X25" t="n">
-        <v>0.9985620171889108</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -31639,20 +31813,24 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>C186T</t>
+          <t>C75A,C8782T,G11083C,T21644A,T28144C</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F,ORF8:L84S,S:Y28N</t>
+        </is>
+      </c>
       <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="inlineStr"/>
       <c r="AH25" t="inlineStr"/>
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>C186T</t>
+          <t>C75A,G11083C,T21644A</t>
         </is>
       </c>
       <c r="AK25" t="n">
@@ -31662,14 +31840,18 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F,S:Y28N</t>
+        </is>
+      </c>
       <c r="AR25" t="n">
         <v>0</v>
       </c>
@@ -31677,37 +31859,45 @@
         <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>C186T</t>
+          <t>C75A,G11083C,T21644A</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F,S:Y28N</t>
+        </is>
+      </c>
       <c r="BA25" t="inlineStr"/>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>C186T</t>
+          <t>C75A,G11083C,T21644A</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr"/>
-      <c r="BE25" t="inlineStr"/>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F,S:Y28N</t>
+        </is>
+      </c>
       <c r="BF25" t="inlineStr"/>
       <c r="BG25" t="inlineStr"/>
       <c r="BH25" t="inlineStr"/>
@@ -31753,7 +31943,7 @@
         <v>24</v>
       </c>
       <c r="CB25" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="CC25" t="n">
         <v>0</v>
@@ -31764,7 +31954,7 @@
         </is>
       </c>
       <c r="CE25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CF25" t="inlineStr"/>
       <c r="CG25" t="n">
@@ -31816,11 +32006,11 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MT039887.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WI-CDC-03041142-001/2020, complete genome</t>
+          <t>MT039873.1 Severe acute respiratory syndrome coronavirus 2 isolate HZ-1, complete genome</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -31858,10 +32048,10 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
@@ -31879,7 +32069,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -31888,16 +32078,16 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>89626</v>
+        <v>89499</v>
       </c>
       <c r="V26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W26" t="n">
-        <v>29882</v>
+        <v>29836</v>
       </c>
       <c r="X26" t="n">
-        <v>0.9992977293248168</v>
+        <v>0.9976590977493895</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -31907,32 +32097,16 @@
       <c r="Z26" t="b">
         <v>0</v>
       </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>C17373T</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>20299-20301</t>
-        </is>
-      </c>
+      <c r="AA26" t="inlineStr"/>
+      <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
       <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>ORF1b:L2278-</t>
-        </is>
-      </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>C17373T</t>
-        </is>
-      </c>
+      <c r="AJ26" t="inlineStr"/>
       <c r="AK26" t="n">
         <v>0</v>
       </c>
@@ -31940,10 +32114,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
@@ -31966,43 +32140,19 @@
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>C17373T</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr">
-        <is>
-          <t>20299-20301</t>
-        </is>
-      </c>
+      <c r="AX26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr"/>
-      <c r="BA26" t="inlineStr">
-        <is>
-          <t>ORF1b:L2278-</t>
-        </is>
-      </c>
+      <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="BC26" t="inlineStr">
-        <is>
-          <t>C17373T</t>
-        </is>
-      </c>
-      <c r="BD26" t="inlineStr">
-        <is>
-          <t>20299-20301</t>
-        </is>
-      </c>
+      <c r="BC26" t="inlineStr"/>
+      <c r="BD26" t="inlineStr"/>
       <c r="BE26" t="inlineStr"/>
-      <c r="BF26" t="inlineStr">
-        <is>
-          <t>ORF1b:L2278-</t>
-        </is>
-      </c>
+      <c r="BF26" t="inlineStr"/>
       <c r="BG26" t="inlineStr"/>
       <c r="BH26" t="inlineStr"/>
       <c r="BI26" t="inlineStr"/>
@@ -32047,7 +32197,7 @@
         <v>24</v>
       </c>
       <c r="CB26" t="n">
-        <v>-6</v>
+        <v>-8</v>
       </c>
       <c r="CC26" t="n">
         <v>0</v>
@@ -32058,7 +32208,7 @@
         </is>
       </c>
       <c r="CE26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CF26" t="inlineStr"/>
       <c r="CG26" t="n">
@@ -32110,37 +32260,37 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MT050493.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/IND/166/2020, complete genome</t>
+          <t>MT020781.2 Severe acute respiratory syndrome coronavirus 2 isolate nCoV-FIN-29-Jan-2020, complete genome</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -32152,7 +32302,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -32170,7 +32320,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -32182,16 +32332,16 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>89529</v>
+        <v>89410</v>
       </c>
       <c r="V27" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>29871</v>
+        <v>29806</v>
       </c>
       <c r="X27" t="n">
-        <v>0.9982610440424038</v>
+        <v>0.9967561783098686</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -32203,7 +32353,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>A1691G,C6501T,C8782T,C16877T,C24351T,T28144C</t>
+          <t>A1C,C21707T</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -32211,7 +32361,7 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,ORF8:L84S,S:A930V</t>
+          <t>S:H49Y</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr"/>
@@ -32220,7 +32370,7 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>A1691G,C6501T,C16877T,C24351T</t>
+          <t>A1C,C21707T</t>
         </is>
       </c>
       <c r="AK27" t="n">
@@ -32230,16 +32380,16 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AN27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,S:A930V</t>
+          <t>S:H49Y</t>
         </is>
       </c>
       <c r="AR27" t="n">
@@ -32249,43 +32399,43 @@
         <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AU27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>A1691G,C6501T,C16877T,C24351T</t>
+          <t>A1C,C21707T</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,S:A930V</t>
+          <t>S:H49Y</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr"/>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>A1691G,C6501T,C16877T,C24351T</t>
+          <t>A1C,C21707T</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr"/>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,S:A930V</t>
+          <t>S:H49Y</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr"/>
@@ -32333,7 +32483,7 @@
         <v>24</v>
       </c>
       <c r="CB27" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="CC27" t="n">
         <v>0</v>
@@ -32344,7 +32494,7 @@
         </is>
       </c>
       <c r="CE27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CF27" t="inlineStr"/>
       <c r="CG27" t="n">
@@ -32396,52 +32546,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MT012098.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/IND/29/2020, complete genome</t>
+          <t>MT044257.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/IL-CDC-03037667-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A.3</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A.3</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>84.027778</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>mediocre</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -32459,7 +32609,7 @@
         <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -32468,16 +32618,16 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>89535</v>
+        <v>89618</v>
       </c>
       <c r="V28" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>29870</v>
+        <v>29882</v>
       </c>
       <c r="X28" t="n">
-        <v>0.9984616928067418</v>
+        <v>0.9992977293248168</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -32489,116 +32639,92 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>T2277C,C6695T,C14657T,C17373T,G22785T</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>21992-21994</t>
-        </is>
-      </c>
+          <t>T490A,C3177T,C8782T,C24034T,T26729C,G28077C,T28144C</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>ORF1a:I671T,ORF1a:P2144S,ORF1b:A397V,S:R408I</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>S:Y144-</t>
-        </is>
-      </c>
+          <t>ORF1a:D75E,ORF1a:P971L,ORF8:V62L,ORF8:L84S</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>T6040C,A12478G,C18736T,G28896C,G29700A</t>
+        </is>
+      </c>
       <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>T2277C,C6695T,C14657T,C17373T,G22785T</t>
-        </is>
-      </c>
+      <c r="AJ28" t="inlineStr"/>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
         <v>5</v>
       </c>
-      <c r="AO28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>N:G208A,ORF1a:I4071M,ORF1b:L1757F</t>
+        </is>
+      </c>
       <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr">
-        <is>
-          <t>ORF1a:I671T,ORF1a:P2144S,ORF1b:A397V,S:R408I</t>
-        </is>
-      </c>
+      <c r="AQ28" t="inlineStr"/>
       <c r="AR28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS28" t="n">
         <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>T2277C,C6695T,C14657T,C17373T,G22785T</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr">
-        <is>
-          <t>21992-21994</t>
-        </is>
-      </c>
+          <t>T490A,C3177T,C24034T,T26729C,G28077C</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>ORF1a:I671T,ORF1a:P2144S,ORF1b:A397V,S:R408I</t>
-        </is>
-      </c>
-      <c r="BA28" t="inlineStr">
-        <is>
-          <t>S:Y144-</t>
-        </is>
-      </c>
+          <t>ORF1a:D75E,ORF1a:P971L,ORF8:V62L</t>
+        </is>
+      </c>
+      <c r="BA28" t="inlineStr"/>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>A.3</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>T2277C,C6695T,C14657T,C17373T,G22785T</t>
-        </is>
-      </c>
-      <c r="BD28" t="inlineStr">
-        <is>
-          <t>21992-21994</t>
-        </is>
-      </c>
+          <t>T6040C,A12478G,C18736T,G28896C,G29700A</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr"/>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>ORF1a:I671T,ORF1a:P2144S,ORF1b:A397V,S:R408I</t>
-        </is>
-      </c>
-      <c r="BF28" t="inlineStr">
-        <is>
-          <t>S:Y144-</t>
-        </is>
-      </c>
+          <t>N:G208A,ORF1a:I4071M,ORF1b:L1757F</t>
+        </is>
+      </c>
+      <c r="BF28" t="inlineStr"/>
       <c r="BG28" t="inlineStr"/>
       <c r="BH28" t="inlineStr"/>
       <c r="BI28" t="inlineStr"/>
@@ -32643,18 +32769,18 @@
         <v>24</v>
       </c>
       <c r="CB28" t="n">
-        <v>-2</v>
+        <v>22</v>
       </c>
       <c r="CC28" t="n">
-        <v>0</v>
+        <v>91.666667</v>
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>mediocre</t>
         </is>
       </c>
       <c r="CE28" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="CF28" t="inlineStr"/>
       <c r="CG28" t="n">
@@ -32706,11 +32832,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MT007544.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/AUS/VIC01/2020, complete genome</t>
+          <t>MT039887.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WI-CDC-03041142-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -32748,11 +32874,11 @@
         </is>
       </c>
       <c r="K29" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" t="n">
         <v>3</v>
       </c>
-      <c r="L29" t="n">
-        <v>10</v>
-      </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
@@ -32766,10 +32892,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -32778,16 +32904,16 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>89661</v>
+        <v>89626</v>
       </c>
       <c r="V29" t="n">
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>29903</v>
+        <v>29882</v>
       </c>
       <c r="X29" t="n">
-        <v>1</v>
+        <v>0.9992977293248168</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -32799,28 +32925,28 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>T19065C,T22303G,G26144T</t>
+          <t>C17373T</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>29750-29759</t>
+          <t>20299-20301</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>ORF3a:G251V,S:S247R</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>ORF1b:L2278-</t>
+        </is>
+      </c>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>T19065C,T22303G,G26144T</t>
+          <t>C17373T</t>
         </is>
       </c>
       <c r="AK29" t="n">
@@ -32830,18 +32956,14 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN29" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr">
-        <is>
-          <t>ORF3a:G251V,S:S247R</t>
-        </is>
-      </c>
+      <c r="AQ29" t="inlineStr"/>
       <c r="AR29" t="n">
         <v>0</v>
       </c>
@@ -32849,10 +32971,10 @@
         <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -32862,20 +32984,20 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>T19065C,T22303G,G26144T</t>
+          <t>C17373T</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>29750-29759</t>
-        </is>
-      </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>ORF3a:G251V,S:S247R</t>
-        </is>
-      </c>
-      <c r="BA29" t="inlineStr"/>
+          <t>20299-20301</t>
+        </is>
+      </c>
+      <c r="AZ29" t="inlineStr"/>
+      <c r="BA29" t="inlineStr">
+        <is>
+          <t>ORF1b:L2278-</t>
+        </is>
+      </c>
       <c r="BB29" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
@@ -32883,20 +33005,20 @@
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>T19065C,T22303G,G26144T</t>
+          <t>C17373T</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>29750-29759</t>
-        </is>
-      </c>
-      <c r="BE29" t="inlineStr">
-        <is>
-          <t>ORF3a:G251V,S:S247R</t>
-        </is>
-      </c>
-      <c r="BF29" t="inlineStr"/>
+          <t>20299-20301</t>
+        </is>
+      </c>
+      <c r="BE29" t="inlineStr"/>
+      <c r="BF29" t="inlineStr">
+        <is>
+          <t>ORF1b:L2278-</t>
+        </is>
+      </c>
       <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr"/>
@@ -32941,7 +33063,7 @@
         <v>24</v>
       </c>
       <c r="CB29" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="CC29" t="n">
         <v>0</v>
@@ -32952,7 +33074,7 @@
         </is>
       </c>
       <c r="CE29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CF29" t="inlineStr"/>
       <c r="CG29" t="n">
@@ -33004,52 +33126,52 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MT044257.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/IL-CDC-03037667-001/2020, complete genome</t>
+          <t>MT007544.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/AUS/VIC01/2020, complete genome</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>A.3</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>A.3</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>84.027778</v>
+        <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>mediocre</t>
+          <t>good</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -33064,7 +33186,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -33076,16 +33198,16 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>89618</v>
+        <v>89661</v>
       </c>
       <c r="V30" t="n">
         <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>29882</v>
+        <v>29903</v>
       </c>
       <c r="X30" t="n">
-        <v>0.9992977293248168</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -33097,89 +33219,101 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>T490A,C3177T,C8782T,C24034T,T26729C,G28077C,T28144C</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr"/>
+          <t>T19065C,T22303G,G26144T</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>29750-29759</t>
+        </is>
+      </c>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>ORF1a:D75E,ORF1a:P971L,ORF8:V62L,ORF8:L84S</t>
+          <t>ORF3a:G251V,S:S247R</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>T6040C,A12478G,C18736T,G28896C,G29700A</t>
-        </is>
-      </c>
+      <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>T19065C,T22303G,G26144T</t>
+        </is>
+      </c>
       <c r="AK30" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN30" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>N:G208A,ORF1a:I4071M,ORF1b:L1757F</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr">
+        <is>
+          <t>ORF3a:G251V,S:S247R</t>
+        </is>
+      </c>
       <c r="AR30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS30" t="n">
         <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>T490A,C3177T,C24034T,T26729C,G28077C</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>T19065C,T22303G,G26144T</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>29750-29759</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>ORF1a:D75E,ORF1a:P971L,ORF8:V62L</t>
+          <t>ORF3a:G251V,S:S247R</t>
         </is>
       </c>
       <c r="BA30" t="inlineStr"/>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>A.3</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>T6040C,A12478G,C18736T,G28896C,G29700A</t>
-        </is>
-      </c>
-      <c r="BD30" t="inlineStr"/>
+          <t>T19065C,T22303G,G26144T</t>
+        </is>
+      </c>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>29750-29759</t>
+        </is>
+      </c>
       <c r="BE30" t="inlineStr">
         <is>
-          <t>N:G208A,ORF1a:I4071M,ORF1b:L1757F</t>
+          <t>ORF3a:G251V,S:S247R</t>
         </is>
       </c>
       <c r="BF30" t="inlineStr"/>
@@ -33227,18 +33361,18 @@
         <v>24</v>
       </c>
       <c r="CB30" t="n">
-        <v>22</v>
+        <v>-4</v>
       </c>
       <c r="CC30" t="n">
-        <v>91.666667</v>
+        <v>0</v>
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>mediocre</t>
+          <t>good</t>
         </is>
       </c>
       <c r="CE30" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="CF30" t="inlineStr"/>
       <c r="CG30" t="n">
@@ -33290,41 +33424,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MT049951.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/Yunnan-01/2020, complete genome</t>
+          <t>MT039890.1 Severe acute respiratory syndrome coronavirus 2 isolate SNU01, complete genome</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.173611</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -33332,7 +33466,7 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -33350,7 +33484,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -33362,7 +33496,7 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>89689</v>
+        <v>89673</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
@@ -33383,7 +33517,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>C75A,C8782T,G11083C,T21644A,T28144C</t>
+          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -33391,7 +33525,7 @@
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,ORF8:L84S,S:Y28N</t>
+          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr"/>
@@ -33400,7 +33534,7 @@
       <c r="AI31" t="inlineStr"/>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>C75A,G11083C,T21644A</t>
+          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
         </is>
       </c>
       <c r="AK31" t="n">
@@ -33410,16 +33544,16 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AN31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="AO31" t="inlineStr"/>
       <c r="AP31" t="inlineStr"/>
       <c r="AQ31" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,S:Y28N</t>
+          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
         </is>
       </c>
       <c r="AR31" t="n">
@@ -33429,43 +33563,43 @@
         <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AU31" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>C75A,G11083C,T21644A</t>
+          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,S:Y28N</t>
+          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr"/>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>C75A,G11083C,T21644A</t>
+          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr"/>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,S:Y28N</t>
+          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr"/>
@@ -33513,10 +33647,10 @@
         <v>24</v>
       </c>
       <c r="CB31" t="n">
-        <v>-5</v>
+        <v>1</v>
       </c>
       <c r="CC31" t="n">
-        <v>0</v>
+        <v>4.166667</v>
       </c>
       <c r="CD31" t="inlineStr">
         <is>
@@ -33524,7 +33658,7 @@
         </is>
       </c>
       <c r="CE31" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="CF31" t="inlineStr"/>
       <c r="CG31" t="n">
@@ -33576,37 +33710,37 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MN997409.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/AZ-CDC-02993465-001/2020, complete genome</t>
+          <t>MT012098.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/IND/29/2020, complete genome</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -33618,28 +33752,28 @@
         </is>
       </c>
       <c r="K32" t="n">
+        <v>5</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
         <v>4</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>2</v>
-      </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -33648,16 +33782,16 @@
         <v>0</v>
       </c>
       <c r="U32" t="n">
-        <v>89630</v>
+        <v>89535</v>
       </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W32" t="n">
-        <v>29882</v>
+        <v>29870</v>
       </c>
       <c r="X32" t="n">
-        <v>0.9992977293248168</v>
+        <v>0.9984616928067418</v>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
@@ -33669,24 +33803,32 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>C8782T,G11083T,T28144C,C29095T</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr"/>
+          <t>T2277C,C6695T,C14657T,C17373T,G22785T</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>21992-21994</t>
+        </is>
+      </c>
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr"/>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,ORF8:L84S</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr"/>
+          <t>ORF1a:I671T,ORF1a:P2144S,ORF1b:A397V,S:R408I</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>S:Y144-</t>
+        </is>
+      </c>
       <c r="AG32" t="inlineStr"/>
       <c r="AH32" t="inlineStr"/>
       <c r="AI32" t="inlineStr"/>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>G11083T,C29095T</t>
+          <t>T2277C,C6695T,C14657T,C17373T,G22785T</t>
         </is>
       </c>
       <c r="AK32" t="n">
@@ -33696,16 +33838,16 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AN32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AO32" t="inlineStr"/>
       <c r="AP32" t="inlineStr"/>
       <c r="AQ32" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F</t>
+          <t>ORF1a:I671T,ORF1a:P2144S,ORF1b:A397V,S:R408I</t>
         </is>
       </c>
       <c r="AR32" t="n">
@@ -33715,46 +33857,62 @@
         <v>0</v>
       </c>
       <c r="AT32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AU32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>G11083T,C29095T</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>T2277C,C6695T,C14657T,C17373T,G22785T</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>21992-21994</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F</t>
-        </is>
-      </c>
-      <c r="BA32" t="inlineStr"/>
+          <t>ORF1a:I671T,ORF1a:P2144S,ORF1b:A397V,S:R408I</t>
+        </is>
+      </c>
+      <c r="BA32" t="inlineStr">
+        <is>
+          <t>S:Y144-</t>
+        </is>
+      </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>G11083T,C29095T</t>
-        </is>
-      </c>
-      <c r="BD32" t="inlineStr"/>
+          <t>T2277C,C6695T,C14657T,C17373T,G22785T</t>
+        </is>
+      </c>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>21992-21994</t>
+        </is>
+      </c>
       <c r="BE32" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F</t>
-        </is>
-      </c>
-      <c r="BF32" t="inlineStr"/>
+          <t>ORF1a:I671T,ORF1a:P2144S,ORF1b:A397V,S:R408I</t>
+        </is>
+      </c>
+      <c r="BF32" t="inlineStr">
+        <is>
+          <t>S:Y144-</t>
+        </is>
+      </c>
       <c r="BG32" t="inlineStr"/>
       <c r="BH32" t="inlineStr"/>
       <c r="BI32" t="inlineStr"/>
@@ -33799,7 +33957,7 @@
         <v>24</v>
       </c>
       <c r="CB32" t="n">
-        <v>-6</v>
+        <v>-2</v>
       </c>
       <c r="CC32" t="n">
         <v>0</v>
@@ -33810,7 +33968,7 @@
         </is>
       </c>
       <c r="CE32" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="CF32" t="inlineStr"/>
       <c r="CG32" t="n">
@@ -33862,11 +34020,11 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MT039890.1 Severe acute respiratory syndrome coronavirus 2 isolate SNU01, complete genome</t>
+          <t>MT066156.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/ITA/INMI1/2020, complete genome</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -33896,7 +34054,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.173611</v>
+        <v>0</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -33904,7 +34062,7 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -33916,13 +34074,13 @@
         <v>0</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -33931,23 +34089,23 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>89673</v>
+        <v>89592</v>
       </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>29903</v>
+        <v>29867</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>0.9987626659532488</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>E:1,M:1,N:1,ORF1a:1,ORF1b:1,ORF3a:1,ORF6:1,ORF7a:1,ORF7b:1,ORF8:1,ORF9b:1,S:1</t>
+          <t>E:1,M:1,N:1,ORF1a:0.9997727789138832,ORF1b:1,ORF3a:1,ORF6:1,ORF7a:1,ORF7b:1,ORF8:1,ORF9b:1,S:1</t>
         </is>
       </c>
       <c r="Z33" t="b">
@@ -33955,7 +34113,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
+          <t>A2269T,G26144T</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -33963,37 +34121,37 @@
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
+          <t>ORF3a:G251V</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>T14805C</t>
+        </is>
+      </c>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
+          <t>A2269T</t>
         </is>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AN33" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr">
-        <is>
-          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
-        </is>
-      </c>
+      <c r="AQ33" t="inlineStr"/>
       <c r="AR33" t="n">
         <v>0</v>
       </c>
@@ -34001,12 +34159,14 @@
         <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AU33" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV33" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>11083</v>
+      </c>
       <c r="AW33" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
@@ -34014,13 +34174,13 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
+          <t>A2269T,G26144T</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
+          <t>ORF3a:G251V</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr"/>
@@ -34031,13 +34191,13 @@
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
+          <t>A2269T,G26144T</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr"/>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
+          <t>ORF3a:G251V</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr"/>
@@ -34051,7 +34211,11 @@
       <c r="BN33" t="inlineStr"/>
       <c r="BO33" t="inlineStr"/>
       <c r="BP33" t="inlineStr"/>
-      <c r="BQ33" t="inlineStr"/>
+      <c r="BQ33" t="inlineStr">
+        <is>
+          <t>ORF1a:3606</t>
+        </is>
+      </c>
       <c r="BR33" t="inlineStr"/>
       <c r="BS33" t="n">
         <v>3000</v>
@@ -34065,7 +34229,7 @@
         </is>
       </c>
       <c r="BV33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW33" t="n">
         <v>10</v>
@@ -34085,10 +34249,10 @@
         <v>24</v>
       </c>
       <c r="CB33" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="CC33" t="n">
-        <v>4.166667</v>
+        <v>0</v>
       </c>
       <c r="CD33" t="inlineStr">
         <is>
@@ -34096,7 +34260,7 @@
         </is>
       </c>
       <c r="CE33" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="CF33" t="inlineStr"/>
       <c r="CG33" t="n">
@@ -34422,37 +34586,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LC529905.1 Severe acute respiratory syndrome coronavirus 2 TKYE6182_2020 RNA, complete genome</t>
+          <t>MN938384.1 Severe acute respiratory syndrome coronavirus 2 isolate 2019-nCoV_HKU-SZ-002a_2020, complete genome</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -34482,7 +34646,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -34494,16 +34658,16 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>89697</v>
+        <v>89502</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="W35" t="n">
-        <v>29903</v>
+        <v>29870</v>
       </c>
       <c r="X35" t="n">
-        <v>1</v>
+        <v>0.9978263050530048</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -34515,7 +34679,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>C15324T,C25810G,C29303T</t>
+          <t>C8782T,T28144C,C29095T</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
@@ -34523,7 +34687,7 @@
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>N:P344S,ORF3a:L140V</t>
+          <t>ORF8:L84S</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr"/>
@@ -34532,7 +34696,7 @@
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>C15324T,C25810G,C29303T</t>
+          <t>C29095T</t>
         </is>
       </c>
       <c r="AK35" t="n">
@@ -34542,18 +34706,14 @@
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO35" t="inlineStr"/>
       <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr">
-        <is>
-          <t>N:P344S,ORF3a:L140V</t>
-        </is>
-      </c>
+      <c r="AQ35" t="inlineStr"/>
       <c r="AR35" t="n">
         <v>0</v>
       </c>
@@ -34561,45 +34721,37 @@
         <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>C15324T,C25810G,C29303T</t>
+          <t>C29095T</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>N:P344S,ORF3a:L140V</t>
-        </is>
-      </c>
+      <c r="AZ35" t="inlineStr"/>
       <c r="BA35" t="inlineStr"/>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>C15324T,C25810G,C29303T</t>
+          <t>C29095T</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr"/>
-      <c r="BE35" t="inlineStr">
-        <is>
-          <t>N:P344S,ORF3a:L140V</t>
-        </is>
-      </c>
+      <c r="BE35" t="inlineStr"/>
       <c r="BF35" t="inlineStr"/>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
@@ -34645,7 +34797,7 @@
         <v>24</v>
       </c>
       <c r="CB35" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="CC35" t="n">
         <v>0</v>
@@ -34656,7 +34808,7 @@
         </is>
       </c>
       <c r="CE35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CF35" t="inlineStr"/>
       <c r="CG35" t="n">
@@ -34708,37 +34860,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MN938384.1 Severe acute respiratory syndrome coronavirus 2 isolate 2019-nCoV_HKU-SZ-002a_2020, complete genome</t>
+          <t>LC529905.1 Severe acute respiratory syndrome coronavirus 2 TKYE6182_2020 RNA, complete genome</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -34768,7 +34920,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -34780,16 +34932,16 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>89502</v>
+        <v>89697</v>
       </c>
       <c r="V36" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>29870</v>
+        <v>29903</v>
       </c>
       <c r="X36" t="n">
-        <v>0.9978263050530048</v>
+        <v>1</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -34801,7 +34953,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>C8782T,T28144C,C29095T</t>
+          <t>C15324T,C25810G,C29303T</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
@@ -34809,7 +34961,7 @@
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>ORF8:L84S</t>
+          <t>N:P344S,ORF3a:L140V</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr"/>
@@ -34818,7 +34970,7 @@
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>C29095T</t>
+          <t>C15324T,C25810G,C29303T</t>
         </is>
       </c>
       <c r="AK36" t="n">
@@ -34828,14 +34980,18 @@
         <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
+      <c r="AQ36" t="inlineStr">
+        <is>
+          <t>N:P344S,ORF3a:L140V</t>
+        </is>
+      </c>
       <c r="AR36" t="n">
         <v>0</v>
       </c>
@@ -34843,37 +34999,45 @@
         <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>C29095T</t>
+          <t>C15324T,C25810G,C29303T</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>N:P344S,ORF3a:L140V</t>
+        </is>
+      </c>
       <c r="BA36" t="inlineStr"/>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>C29095T</t>
+          <t>C15324T,C25810G,C29303T</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr"/>
-      <c r="BE36" t="inlineStr"/>
+      <c r="BE36" t="inlineStr">
+        <is>
+          <t>N:P344S,ORF3a:L140V</t>
+        </is>
+      </c>
       <c r="BF36" t="inlineStr"/>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
@@ -34919,7 +35083,7 @@
         <v>24</v>
       </c>
       <c r="CB36" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="CC36" t="n">
         <v>0</v>
@@ -34930,7 +35094,7 @@
         </is>
       </c>
       <c r="CE36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CF36" t="inlineStr"/>
       <c r="CG36" t="n">

--- a/results/genbank_table.xlsx
+++ b/results/genbank_table.xlsx
@@ -10,9 +10,8 @@
     <sheet name="Metadata_counts" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="CDS_features" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Sequences" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mutations" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="QC_summary" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Nextclade_results" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="QC_summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Nextclade_results" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21727,2741 +21726,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L64"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="38" customWidth="1" min="8" max="8"/>
-    <col width="31" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="57" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>sample_accession</t>
+          <t>metric</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>reference_accession</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>position</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ref_base</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>sample_base</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>mutation</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>gene</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>product</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>protein_id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>is_in_cds</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>comparison_note</t>
+          <t>value</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MN938384</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-      <c r="K2" t="b">
-        <v>1</v>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>sample length 29838 differs from reference length 29903</t>
-        </is>
+          <t>record_count</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MN985325</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-      <c r="K3" t="b">
-        <v>1</v>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>sample length 29882 differs from reference length 29903</t>
-        </is>
+          <t>cds_count</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>358</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MN997409</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="b">
-        <v>0</v>
-      </c>
-      <c r="K4" t="b">
-        <v>1</v>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>sample length 29882 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MT007544</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="b">
-        <v>0</v>
-      </c>
-      <c r="K5" t="b">
-        <v>1</v>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>sample length 29893 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MT012098</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="b">
-        <v>0</v>
-      </c>
-      <c r="K6" t="b">
-        <v>1</v>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>sample length 29854 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>MT039873</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="b">
-        <v>0</v>
-      </c>
-      <c r="K7" t="b">
-        <v>1</v>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>sample length 29833 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MT039890</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>2971</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>G2971T</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein;ORF1a polyprotein</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>YP_009724389.1;YP_009725295.1</t>
-        </is>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
-      <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MT039890</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>6031</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>C6031T</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein;ORF1a polyprotein</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>YP_009724389.1;YP_009725295.1</t>
-        </is>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
-      <c r="K9" t="b">
-        <v>0</v>
-      </c>
-      <c r="L9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MT039890</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>12115</v>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>C12115T</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein;ORF1a polyprotein</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>YP_009724389.1;YP_009725295.1</t>
-        </is>
-      </c>
-      <c r="J10" t="b">
-        <v>1</v>
-      </c>
-      <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MT039890</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>15597</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>T15597C</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>YP_009724389.1</t>
-        </is>
-      </c>
-      <c r="J11" t="b">
-        <v>1</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-      <c r="L11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MT039890</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>20936</v>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>C20936T</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>YP_009724389.1</t>
-        </is>
-      </c>
-      <c r="J12" t="b">
-        <v>1</v>
-      </c>
-      <c r="K12" t="b">
-        <v>0</v>
-      </c>
-      <c r="L12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MT039890</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>22224</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>C22224G</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>surface glycoprotein</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>YP_009724390.1</t>
-        </is>
-      </c>
-      <c r="J13" t="b">
-        <v>1</v>
-      </c>
-      <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MT039890</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>25775</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>G25775T</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ORF3a</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>ORF3a protein</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>YP_009724391.1</t>
-        </is>
-      </c>
-      <c r="J14" t="b">
-        <v>1</v>
-      </c>
-      <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MT039890</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>26144</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>G26144T</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>ORF3a</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>ORF3a protein</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>YP_009724391.1</t>
-        </is>
-      </c>
-      <c r="J15" t="b">
-        <v>1</v>
-      </c>
-      <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MT039890</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>26354</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>T26354A</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>envelope protein</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>YP_009724392.1</t>
-        </is>
-      </c>
-      <c r="J16" t="b">
-        <v>1</v>
-      </c>
-      <c r="K16" t="b">
-        <v>0</v>
-      </c>
-      <c r="L16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MT039887</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="b">
-        <v>0</v>
-      </c>
-      <c r="K17" t="b">
-        <v>1</v>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>sample length 29879 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>MT044257</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="b">
-        <v>0</v>
-      </c>
-      <c r="K18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>sample length 29882 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>MT049951</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>75</v>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>C75A</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="b">
-        <v>0</v>
-      </c>
-      <c r="K19" t="b">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>MT049951</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>8782</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>C8782T</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein;ORF1a polyprotein</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>YP_009724389.1;YP_009725295.1</t>
-        </is>
-      </c>
-      <c r="J20" t="b">
-        <v>1</v>
-      </c>
-      <c r="K20" t="b">
-        <v>0</v>
-      </c>
-      <c r="L20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>MT049951</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>11083</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>G11083C</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein;ORF1a polyprotein</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>YP_009724389.1;YP_009725295.1</t>
-        </is>
-      </c>
-      <c r="J21" t="b">
-        <v>1</v>
-      </c>
-      <c r="K21" t="b">
-        <v>0</v>
-      </c>
-      <c r="L21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>MT049951</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>21644</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>T21644A</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>surface glycoprotein</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>YP_009724390.1</t>
-        </is>
-      </c>
-      <c r="J22" t="b">
-        <v>1</v>
-      </c>
-      <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>MT049951</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>28144</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>T28144C</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ORF8</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>ORF8 protein</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>YP_009724396.1</t>
-        </is>
-      </c>
-      <c r="J23" t="b">
-        <v>1</v>
-      </c>
-      <c r="K23" t="b">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>MT050493</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="b">
-        <v>0</v>
-      </c>
-      <c r="K24" t="b">
-        <v>1</v>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>sample length 29851 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>MT066156</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="b">
-        <v>0</v>
-      </c>
-      <c r="K25" t="b">
-        <v>1</v>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>sample length 29867 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>MT066175</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="b">
-        <v>0</v>
-      </c>
-      <c r="K26" t="b">
-        <v>1</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>sample length 29870 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>MT072688</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="b">
-        <v>0</v>
-      </c>
-      <c r="K27" t="b">
-        <v>1</v>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>sample length 29811 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>MT093571</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="b">
-        <v>0</v>
-      </c>
-      <c r="K28" t="b">
-        <v>1</v>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>sample length 29886 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>MT123290</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="b">
-        <v>0</v>
-      </c>
-      <c r="K29" t="b">
-        <v>1</v>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>sample length 29891 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>MT126808</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="b">
-        <v>0</v>
-      </c>
-      <c r="K30" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>sample length 29876 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>MT135044</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>4402</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>T4402C</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein;ORF1a polyprotein</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>YP_009724389.1;YP_009725295.1</t>
-        </is>
-      </c>
-      <c r="J31" t="b">
-        <v>1</v>
-      </c>
-      <c r="K31" t="b">
-        <v>0</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>MT135044</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>5062</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>G5062T</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein;ORF1a polyprotein</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>YP_009724389.1;YP_009725295.1</t>
-        </is>
-      </c>
-      <c r="J32" t="b">
-        <v>1</v>
-      </c>
-      <c r="K32" t="b">
-        <v>0</v>
-      </c>
-      <c r="L32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>MT135044</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>8782</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>C8782T</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein;ORF1a polyprotein</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>YP_009724389.1;YP_009725295.1</t>
-        </is>
-      </c>
-      <c r="J33" t="b">
-        <v>1</v>
-      </c>
-      <c r="K33" t="b">
-        <v>0</v>
-      </c>
-      <c r="L33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>MT135044</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>28144</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>T28144C</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>ORF8</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>ORF8 protein</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>YP_009724396.1</t>
-        </is>
-      </c>
-      <c r="J34" t="b">
-        <v>1</v>
-      </c>
-      <c r="K34" t="b">
-        <v>0</v>
-      </c>
-      <c r="L34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>MT152824</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="b">
-        <v>0</v>
-      </c>
-      <c r="K35" t="b">
-        <v>1</v>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>sample length 29878 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>MT121215</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="b">
-        <v>0</v>
-      </c>
-      <c r="K36" t="b">
-        <v>1</v>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>sample length 29945 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>1</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>A1T</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="b">
-        <v>0</v>
-      </c>
-      <c r="K37" t="b">
-        <v>0</v>
-      </c>
-      <c r="L37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>35</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>A35T</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="b">
-        <v>0</v>
-      </c>
-      <c r="K38" t="b">
-        <v>0</v>
-      </c>
-      <c r="L38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>36</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>C36T</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="b">
-        <v>0</v>
-      </c>
-      <c r="K39" t="b">
-        <v>0</v>
-      </c>
-      <c r="L39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>2446</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>T2446C</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein;ORF1a polyprotein</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>YP_009724389.1;YP_009725295.1</t>
-        </is>
-      </c>
-      <c r="J40" t="b">
-        <v>1</v>
-      </c>
-      <c r="K40" t="b">
-        <v>0</v>
-      </c>
-      <c r="L40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>3411</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>C3411T</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein;ORF1a polyprotein</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>YP_009724389.1;YP_009725295.1</t>
-        </is>
-      </c>
-      <c r="J41" t="b">
-        <v>1</v>
-      </c>
-      <c r="K41" t="b">
-        <v>0</v>
-      </c>
-      <c r="L41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>5572</v>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>G5572T</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein;ORF1a polyprotein</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>YP_009724389.1;YP_009725295.1</t>
-        </is>
-      </c>
-      <c r="J42" t="b">
-        <v>1</v>
-      </c>
-      <c r="K42" t="b">
-        <v>0</v>
-      </c>
-      <c r="L42" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>11083</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>G11083T</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein;ORF1a polyprotein</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>YP_009724389.1;YP_009725295.1</t>
-        </is>
-      </c>
-      <c r="J43" t="b">
-        <v>1</v>
-      </c>
-      <c r="K43" t="b">
-        <v>0</v>
-      </c>
-      <c r="L43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>14805</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>C14805T</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>YP_009724389.1</t>
-        </is>
-      </c>
-      <c r="J44" t="b">
-        <v>1</v>
-      </c>
-      <c r="K44" t="b">
-        <v>0</v>
-      </c>
-      <c r="L44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>26144</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>G26144T</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>ORF3a</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>ORF3a protein</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>YP_009724391.1</t>
-        </is>
-      </c>
-      <c r="J45" t="b">
-        <v>1</v>
-      </c>
-      <c r="K45" t="b">
-        <v>0</v>
-      </c>
-      <c r="L45" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>29864</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>G29864A</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="b">
-        <v>0</v>
-      </c>
-      <c r="K46" t="b">
-        <v>0</v>
-      </c>
-      <c r="L46" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>29867</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>T29867A</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="b">
-        <v>0</v>
-      </c>
-      <c r="K47" t="b">
-        <v>0</v>
-      </c>
-      <c r="L47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>29868</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>G29868A</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="b">
-        <v>0</v>
-      </c>
-      <c r="K48" t="b">
-        <v>0</v>
-      </c>
-      <c r="L48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>MT163716</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>29870</v>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>C29870A</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="b">
-        <v>0</v>
-      </c>
-      <c r="K49" t="b">
-        <v>0</v>
-      </c>
-      <c r="L49" t="inlineStr"/>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>MT163720</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="b">
-        <v>0</v>
-      </c>
-      <c r="K50" t="b">
-        <v>1</v>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>sample length 29732 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>LC529905</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>15324</v>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>C15324T</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>ORF1ab</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>ORF1ab polyprotein</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>YP_009724389.1</t>
-        </is>
-      </c>
-      <c r="J51" t="b">
-        <v>1</v>
-      </c>
-      <c r="K51" t="b">
-        <v>0</v>
-      </c>
-      <c r="L51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>LC529905</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>25810</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>C25810G</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>ORF3a</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>ORF3a protein</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>YP_009724391.1</t>
-        </is>
-      </c>
-      <c r="J52" t="b">
-        <v>1</v>
-      </c>
-      <c r="K52" t="b">
-        <v>0</v>
-      </c>
-      <c r="L52" t="inlineStr"/>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>LC529905</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>29303</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>T</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>C29303T</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>nucleocapsid phosphoprotein</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>YP_009724397.2</t>
-        </is>
-      </c>
-      <c r="J53" t="b">
-        <v>1</v>
-      </c>
-      <c r="K53" t="b">
-        <v>0</v>
-      </c>
-      <c r="L53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>MT093631</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="b">
-        <v>0</v>
-      </c>
-      <c r="K54" t="b">
-        <v>1</v>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>sample length 29860 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>MT123293</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="b">
-        <v>0</v>
-      </c>
-      <c r="K55" t="b">
-        <v>1</v>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>sample length 29871 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>MT188341</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="b">
-        <v>0</v>
-      </c>
-      <c r="K56" t="b">
-        <v>1</v>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>sample length 29835 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>MT192759</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="b">
-        <v>0</v>
-      </c>
-      <c r="K57" t="b">
-        <v>1</v>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>sample length 29862 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>MT192765</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="b">
-        <v>0</v>
-      </c>
-      <c r="K58" t="b">
-        <v>1</v>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>sample length 29829 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>MT192772</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="b">
-        <v>0</v>
-      </c>
-      <c r="K59" t="b">
-        <v>1</v>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t>sample length 29891 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>MT192773</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="b">
-        <v>0</v>
-      </c>
-      <c r="K60" t="b">
-        <v>1</v>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>sample length 29890 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>MT020781</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="b">
-        <v>0</v>
-      </c>
-      <c r="K61" t="b">
-        <v>1</v>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>sample length 29806 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>MT159716</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="b">
-        <v>0</v>
-      </c>
-      <c r="K62" t="b">
-        <v>1</v>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>sample length 29867 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>MT159718</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="b">
-        <v>0</v>
-      </c>
-      <c r="K63" t="b">
-        <v>1</v>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>sample length 29882 differs from reference length 29903</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>MT184908</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>requires_alignment</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="b">
-        <v>0</v>
-      </c>
-      <c r="K64" t="b">
-        <v>1</v>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>sample length 29882 differs from reference length 29903</t>
-        </is>
+          <t>records_with_N</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -24470,120 +21781,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>metric</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>reference_accession</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>NC_045512</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>reference_accession_version</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>NC_045512.2</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>record_count</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>cds_count</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>records_with_N</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>records_with_length_different_from_reference</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>mutation_count</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>records_requiring_alignment</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>29</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -25210,11 +22407,11 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MT192773.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/VNM/nCoV-19-02S/2020, complete genome</t>
+          <t>NC_045512.2 Severe acute respiratory syndrome coronavirus 2 isolate Wuhan-Hu-1, complete genome</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -25252,10 +22449,10 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -25270,7 +22467,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -25282,16 +22479,16 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>89656</v>
+        <v>89709</v>
       </c>
       <c r="V2" t="n">
         <v>1</v>
       </c>
       <c r="W2" t="n">
-        <v>29891</v>
+        <v>29903</v>
       </c>
       <c r="X2" t="n">
-        <v>0.999598702471324</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -25301,32 +22498,16 @@
       <c r="Z2" t="b">
         <v>0</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>C28T,C10232T</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>ORF1a:R3323C</t>
-        </is>
-      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>C28T,C10232T</t>
-        </is>
-      </c>
+      <c r="AJ2" t="inlineStr"/>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
@@ -25334,18 +22515,14 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>ORF1a:R3323C</t>
-        </is>
-      </c>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
@@ -25353,10 +22530,10 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -25364,42 +22541,18 @@
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>C28T,C10232T</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>ORF1a:R3323C</t>
-        </is>
-      </c>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>C28T,C10232T</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>ORF1a:R3323C</t>
-        </is>
-      </c>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
       <c r="BF2" t="inlineStr"/>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
@@ -25445,7 +22598,7 @@
         <v>24</v>
       </c>
       <c r="CB2" t="n">
-        <v>-5</v>
+        <v>-8</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
@@ -25456,7 +22609,7 @@
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="CF2" t="inlineStr"/>
       <c r="CG2" t="n">
@@ -25508,37 +22661,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MT152824.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA2/2020, complete genome</t>
+          <t>MT192759.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/TWN/CGMH-CGU-01/2020, complete genome</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -25550,7 +22703,7 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -25568,7 +22721,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -25580,16 +22733,16 @@
         <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>89610</v>
+        <v>89586</v>
       </c>
       <c r="V3" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="W3" t="n">
-        <v>29880</v>
+        <v>29889</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9991639634819248</v>
+        <v>0.9986289001103568</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -25599,28 +22752,16 @@
       <c r="Z3" t="b">
         <v>0</v>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>C5784T,C8782T,C17747T,A17858G,C18060T,T28144C</t>
-        </is>
-      </c>
+      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C,ORF8:L84S</t>
-        </is>
-      </c>
+      <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>C5784T</t>
-        </is>
-      </c>
+      <c r="AJ3" t="inlineStr"/>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
@@ -25628,18 +22769,14 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO3" t="inlineStr"/>
       <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>ORF1a:T1840I</t>
-        </is>
-      </c>
+      <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
         <v>0</v>
       </c>
@@ -25647,45 +22784,29 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>internal_b384</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>C5784T,C17747T,A17858G,C18060T</t>
-        </is>
-      </c>
+          <t>NODE_0000000</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr"/>
       <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C</t>
-        </is>
-      </c>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>A.1</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>C5784T</t>
-        </is>
-      </c>
+          <t>NODE_0000000</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr"/>
       <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>ORF1a:T1840I</t>
-        </is>
-      </c>
+      <c r="BE3" t="inlineStr"/>
       <c r="BF3" t="inlineStr"/>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
@@ -25731,7 +22852,7 @@
         <v>24</v>
       </c>
       <c r="CB3" t="n">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="CC3" t="n">
         <v>0</v>
@@ -25742,7 +22863,7 @@
         </is>
       </c>
       <c r="CE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="inlineStr"/>
       <c r="CG3" t="n">
@@ -25794,37 +22915,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MT192772.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/VNM/nCoV-19-01S/2020, complete genome</t>
+          <t>MT163720.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA8-UW5/2020, complete genome</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -25836,7 +22957,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -25854,7 +22975,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -25866,16 +22987,16 @@
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>89669</v>
+        <v>89164</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>172</v>
       </c>
       <c r="W4" t="n">
-        <v>29891</v>
+        <v>29903</v>
       </c>
       <c r="X4" t="n">
-        <v>0.999598702471324</v>
+        <v>0.9942815102163662</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -25887,7 +23008,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>C10232T</t>
+          <t>A3406C,C5784T,C8782T,C17747T,A17858G,C18060T,C23525T,T28144C</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr"/>
@@ -25895,35 +23016,39 @@
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>ORF1a:R3323C</t>
+          <t>ORF1a:E1047D,ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C,ORF8:L84S,S:H655Y</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>C23525T|21K&amp;21L&amp;22B&amp;22E&amp;23A&amp;22C&amp;24A&amp;22A&amp;23F&amp;23D&amp;20J&amp;23B&amp;22D&amp;24E&amp;22F&amp;rec&amp;25C&amp;23C&amp;24C&amp;24F&amp;23E&amp;24B&amp;23H&amp;25B&amp;25A&amp;23I&amp;24G&amp;23G&amp;24H&amp;24D&amp;21M&amp;25D&amp;24I&amp;25G&amp;25E&amp;25I&amp;25H&amp;25F</t>
+        </is>
+      </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>C10232T</t>
+          <t>A3406C,C5784T</t>
         </is>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO4" t="inlineStr"/>
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>ORF1a:R3323C</t>
+          <t>ORF1a:E1047D,ORF1a:T1840I,S:H655Y</t>
         </is>
       </c>
       <c r="AR4" t="n">
@@ -25933,43 +23058,43 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AV4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>C10232T</t>
+          <t>A3406C,C5784T,C17747T,A17858G,C18060T,C23525T</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>ORF1a:R3323C</t>
+          <t>ORF1a:E1047D,ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C,S:H655Y</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr"/>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>C10232T</t>
+          <t>A3406C,C5784T,C23525T</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr"/>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>ORF1a:R3323C</t>
+          <t>ORF1a:E1047D,ORF1a:T1840I,S:H655Y</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr"/>
@@ -26017,7 +23142,7 @@
         <v>24</v>
       </c>
       <c r="CB4" t="n">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="CC4" t="n">
         <v>0</v>
@@ -26028,7 +23153,7 @@
         </is>
       </c>
       <c r="CE4" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="CF4" t="inlineStr"/>
       <c r="CG4" t="n">
@@ -26080,41 +23205,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MT163716.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA3-UW1/2020, complete genome</t>
+          <t>MT192765.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/PC00101P/2020, complete genome</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>20A</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>20A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>20A</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B.1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>B.1</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.694444</v>
+        <v>0</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -26122,7 +23247,7 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -26140,7 +23265,7 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -26152,16 +23277,16 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>89657</v>
+        <v>89467</v>
       </c>
       <c r="V5" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="W5" t="n">
-        <v>29903</v>
+        <v>29836</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0.9975253319064976</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -26173,7 +23298,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G11083T,C14805T,G26144T,G29864A,T29867A,G29868A,C29870A</t>
+          <t>C241T,C3037T,C14408T,C18814T,A23403G</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr"/>
@@ -26181,7 +23306,7 @@
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>ORF1a:A1049V,ORF1a:M1769I,ORF1a:L3606F,ORF3a:G251V</t>
+          <t>ORF1b:P314L,S:D614G</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr"/>
@@ -26190,7 +23315,7 @@
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G29864A,T29867A,G29868A,C29870A</t>
+          <t>C18814T</t>
         </is>
       </c>
       <c r="AK5" t="n">
@@ -26200,18 +23325,14 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr"/>
       <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>ORF1a:A1049V,ORF1a:M1769I</t>
-        </is>
-      </c>
+      <c r="AQ5" t="inlineStr"/>
       <c r="AR5" t="n">
         <v>0</v>
       </c>
@@ -26219,45 +23340,37 @@
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>NODE_0000764</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G11083T,C14805T,G26144T,G29864A,T29867A,G29868A,C29870A</t>
+          <t>C18814T</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>ORF1a:A1049V,ORF1a:M1769I,ORF1a:L3606F,ORF3a:G251V</t>
-        </is>
-      </c>
+      <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>NODE_0000764</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G11083T,C14805T,G26144T,G29864A,T29867A,G29868A,C29870A</t>
+          <t>C18814T</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>ORF1a:A1049V,ORF1a:M1769I,ORF1a:L3606F,ORF3a:G251V</t>
-        </is>
-      </c>
+      <c r="BE5" t="inlineStr"/>
       <c r="BF5" t="inlineStr"/>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
@@ -26303,10 +23416,10 @@
         <v>24</v>
       </c>
       <c r="CB5" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="CC5" t="n">
-        <v>8.333333</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
@@ -26314,7 +23427,7 @@
         </is>
       </c>
       <c r="CE5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="CF5" t="inlineStr"/>
       <c r="CG5" t="n">
@@ -26366,37 +23479,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MT192759.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/TWN/CGMH-CGU-01/2020, complete genome</t>
+          <t>MT152824.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA2/2020, complete genome</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -26408,7 +23521,7 @@
         </is>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -26426,7 +23539,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -26438,16 +23551,16 @@
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>89586</v>
+        <v>89610</v>
       </c>
       <c r="V6" t="n">
-        <v>28</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
-        <v>29889</v>
+        <v>29880</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9986289001103568</v>
+        <v>0.9991639634819248</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -26457,16 +23570,28 @@
       <c r="Z6" t="b">
         <v>0</v>
       </c>
-      <c r="AA6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>C5784T,C8782T,C17747T,A17858G,C18060T,T28144C</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C,ORF8:L84S</t>
+        </is>
+      </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>C5784T</t>
+        </is>
+      </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
@@ -26474,14 +23599,18 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO6" t="inlineStr"/>
       <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>ORF1a:T1840I</t>
+        </is>
+      </c>
       <c r="AR6" t="n">
         <v>0</v>
       </c>
@@ -26489,29 +23618,45 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>internal_b384</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>C5784T,C17747T,A17858G,C18060T</t>
+        </is>
+      </c>
       <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C</t>
+        </is>
+      </c>
       <c r="BA6" t="inlineStr"/>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr"/>
+          <t>A.1</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>C5784T</t>
+        </is>
+      </c>
       <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>ORF1a:T1840I</t>
+        </is>
+      </c>
       <c r="BF6" t="inlineStr"/>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
@@ -26557,7 +23702,7 @@
         <v>24</v>
       </c>
       <c r="CB6" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="CC6" t="n">
         <v>0</v>
@@ -26568,7 +23713,7 @@
         </is>
       </c>
       <c r="CE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF6" t="inlineStr"/>
       <c r="CG6" t="n">
@@ -26620,11 +23765,11 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MT184908.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/Cruise-CDC-3054886-001/2020, complete genome</t>
+          <t>MT192773.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/VNM/nCoV-19-02S/2020, complete genome</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -26662,10 +23807,10 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -26692,16 +23837,16 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>89630</v>
+        <v>89656</v>
       </c>
       <c r="V7" t="n">
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>29882</v>
+        <v>29891</v>
       </c>
       <c r="X7" t="n">
-        <v>0.9992977293248168</v>
+        <v>0.999598702471324</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -26713,15 +23858,19 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>C254T,G11083T,G29736T,G29751C</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr"/>
+          <t>C28T,C10232T</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F</t>
+          <t>ORF1a:R3323C</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr"/>
@@ -26730,7 +23879,7 @@
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>C254T,G29736T,G29751C</t>
+          <t>C28T,C10232T</t>
         </is>
       </c>
       <c r="AK7" t="n">
@@ -26740,14 +23889,18 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AN7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO7" t="inlineStr"/>
       <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>ORF1a:R3323C</t>
+        </is>
+      </c>
       <c r="AR7" t="n">
         <v>0</v>
       </c>
@@ -26755,10 +23908,10 @@
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -26768,13 +23921,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>C254T,G11083T,G29736T,G29751C</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
+          <t>C28T,C10232T</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F</t>
+          <t>ORF1a:R3323C</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr"/>
@@ -26785,13 +23942,17 @@
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>C254T,G11083T,G29736T,G29751C</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr"/>
+          <t>C28T,C10232T</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F</t>
+          <t>ORF1a:R3323C</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr"/>
@@ -26902,11 +24063,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NC_045512.2 Severe acute respiratory syndrome coronavirus 2 isolate Wuhan-Hu-1, complete genome</t>
+          <t>MT123293.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/IQTC03/2020, complete genome</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -26944,7 +24105,7 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -26962,7 +24123,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -26974,16 +24135,16 @@
         <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>89709</v>
+        <v>89593</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="W8" t="n">
-        <v>29903</v>
+        <v>29877</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0.998929873256864</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -26993,16 +24154,28 @@
       <c r="Z8" t="b">
         <v>0</v>
       </c>
-      <c r="AA8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>G654A,G6819T,T6996C,C17373T,G29527A</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>ORF1a:G130E,ORF1a:S2185I,ORF1a:I2244T</t>
+        </is>
+      </c>
       <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>G654A,G6819T,T6996C,C17373T,G29527A</t>
+        </is>
+      </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
@@ -27010,14 +24183,18 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AO8" t="inlineStr"/>
       <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>ORF1a:G130E,ORF1a:S2185I,ORF1a:I2244T</t>
+        </is>
+      </c>
       <c r="AR8" t="n">
         <v>0</v>
       </c>
@@ -27025,10 +24202,10 @@
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AV8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -27036,18 +24213,34 @@
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>G654A,G6819T,T6996C,C17373T,G29527A</t>
+        </is>
+      </c>
       <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>ORF1a:G130E,ORF1a:S2185I,ORF1a:I2244T</t>
+        </is>
+      </c>
       <c r="BA8" t="inlineStr"/>
       <c r="BB8" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>G654A,G6819T,T6996C,C17373T,G29527A</t>
+        </is>
+      </c>
       <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>ORF1a:G130E,ORF1a:S2185I,ORF1a:I2244T</t>
+        </is>
+      </c>
       <c r="BF8" t="inlineStr"/>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
@@ -27093,7 +24286,7 @@
         <v>24</v>
       </c>
       <c r="CB8" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="CC8" t="n">
         <v>0</v>
@@ -27104,7 +24297,7 @@
         </is>
       </c>
       <c r="CE8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CF8" t="inlineStr"/>
       <c r="CG8" t="n">
@@ -27156,37 +24349,37 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MT135044.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/235/2020, complete genome</t>
+          <t>MT192772.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/VNM/nCoV-19-01S/2020, complete genome</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -27198,7 +24391,7 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -27216,7 +24409,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -27228,16 +24421,16 @@
         <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>89693</v>
+        <v>89669</v>
       </c>
       <c r="V9" t="n">
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>29903</v>
+        <v>29891</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0.999598702471324</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -27249,7 +24442,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>T4402C,G5062T,C8782T,T28144C</t>
+          <t>C10232T</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr"/>
@@ -27257,7 +24450,7 @@
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>ORF1a:L1599F,ORF8:L84S</t>
+          <t>ORF1a:R3323C</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr"/>
@@ -27266,7 +24459,7 @@
       <c r="AI9" t="inlineStr"/>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>T4402C,G5062T</t>
+          <t>C10232T</t>
         </is>
       </c>
       <c r="AK9" t="n">
@@ -27276,16 +24469,16 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO9" t="inlineStr"/>
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>ORF1a:L1599F</t>
+          <t>ORF1a:R3323C</t>
         </is>
       </c>
       <c r="AR9" t="n">
@@ -27303,35 +24496,35 @@
       <c r="AV9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>T4402C,G5062T</t>
+          <t>C10232T</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>ORF1a:L1599F</t>
+          <t>ORF1a:R3323C</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr"/>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>T4402C,G5062T</t>
+          <t>C10232T</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr"/>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>ORF1a:L1599F</t>
+          <t>ORF1a:R3323C</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr"/>
@@ -27379,7 +24572,7 @@
         <v>24</v>
       </c>
       <c r="CB9" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="CC9" t="n">
         <v>0</v>
@@ -27390,7 +24583,7 @@
         </is>
       </c>
       <c r="CE9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CF9" t="inlineStr"/>
       <c r="CG9" t="n">
@@ -27442,11 +24635,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MT126808.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/BRA/SP02/2020, complete genome</t>
+          <t>MT184908.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/Cruise-CDC-3054886-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -27502,7 +24695,7 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -27514,16 +24707,16 @@
         <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>89612</v>
+        <v>89630</v>
       </c>
       <c r="V10" t="n">
         <v>1</v>
       </c>
       <c r="W10" t="n">
-        <v>29876</v>
+        <v>29882</v>
       </c>
       <c r="X10" t="n">
-        <v>0.9990970805604787</v>
+        <v>0.9992977293248168</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -27535,7 +24728,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>G11083T,C14805T,T17247C,G26144T</t>
+          <t>C254T,G11083T,G29736T,G29751C</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr"/>
@@ -27543,7 +24736,7 @@
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,ORF3a:G251V</t>
+          <t>ORF1a:L3606F</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr"/>
@@ -27552,7 +24745,7 @@
       <c r="AI10" t="inlineStr"/>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>T17247C</t>
+          <t>C254T,G29736T,G29751C</t>
         </is>
       </c>
       <c r="AK10" t="n">
@@ -27562,10 +24755,10 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO10" t="inlineStr"/>
       <c r="AP10" t="inlineStr"/>
@@ -27590,13 +24783,13 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>G11083T,C14805T,T17247C,G26144T</t>
+          <t>C254T,G11083T,G29736T,G29751C</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,ORF3a:G251V</t>
+          <t>ORF1a:L3606F</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr"/>
@@ -27607,13 +24800,13 @@
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>G11083T,C14805T,T17247C,G26144T</t>
+          <t>C254T,G11083T,G29736T,G29751C</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr"/>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,ORF3a:G251V</t>
+          <t>ORF1a:L3606F</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr"/>
@@ -27661,7 +24854,7 @@
         <v>24</v>
       </c>
       <c r="CB10" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="CC10" t="n">
         <v>0</v>
@@ -27672,7 +24865,7 @@
         </is>
       </c>
       <c r="CE10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CF10" t="inlineStr"/>
       <c r="CG10" t="n">
@@ -27724,11 +24917,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MT123293.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/IQTC03/2020, complete genome</t>
+          <t>MT126808.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/BRA/SP02/2020, complete genome</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -27766,7 +24959,7 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -27784,7 +24977,7 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -27796,16 +24989,16 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>89593</v>
+        <v>89612</v>
       </c>
       <c r="V11" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>29877</v>
+        <v>29876</v>
       </c>
       <c r="X11" t="n">
-        <v>0.998929873256864</v>
+        <v>0.9990970805604787</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -27817,7 +25010,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>G654A,G6819T,T6996C,C17373T,G29527A</t>
+          <t>G11083T,C14805T,T17247C,G26144T</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr"/>
@@ -27825,7 +25018,7 @@
       <c r="AD11" t="inlineStr"/>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>ORF1a:G130E,ORF1a:S2185I,ORF1a:I2244T</t>
+          <t>ORF1a:L3606F,ORF3a:G251V</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr"/>
@@ -27834,7 +25027,7 @@
       <c r="AI11" t="inlineStr"/>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>G654A,G6819T,T6996C,C17373T,G29527A</t>
+          <t>T17247C</t>
         </is>
       </c>
       <c r="AK11" t="n">
@@ -27844,18 +25037,14 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AN11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="inlineStr"/>
       <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>ORF1a:G130E,ORF1a:S2185I,ORF1a:I2244T</t>
-        </is>
-      </c>
+      <c r="AQ11" t="inlineStr"/>
       <c r="AR11" t="n">
         <v>0</v>
       </c>
@@ -27863,10 +25052,10 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AV11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -27876,13 +25065,13 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>G654A,G6819T,T6996C,C17373T,G29527A</t>
+          <t>G11083T,C14805T,T17247C,G26144T</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>ORF1a:G130E,ORF1a:S2185I,ORF1a:I2244T</t>
+          <t>ORF1a:L3606F,ORF3a:G251V</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr"/>
@@ -27893,13 +25082,13 @@
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>G654A,G6819T,T6996C,C17373T,G29527A</t>
+          <t>G11083T,C14805T,T17247C,G26144T</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr"/>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>ORF1a:G130E,ORF1a:S2185I,ORF1a:I2244T</t>
+          <t>ORF1a:L3606F,ORF3a:G251V</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr"/>
@@ -27947,7 +25136,7 @@
         <v>24</v>
       </c>
       <c r="CB11" t="n">
-        <v>-3</v>
+        <v>-7</v>
       </c>
       <c r="CC11" t="n">
         <v>0</v>
@@ -27958,7 +25147,7 @@
         </is>
       </c>
       <c r="CE11" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="CF11" t="inlineStr"/>
       <c r="CG11" t="n">
@@ -28010,41 +25199,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>MT192765.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/PC00101P/2020, complete genome</t>
+          <t>MT188341.1 Severe acute respiratory syndrome coronavirus 2 isolate USA/MN1-MDH1/2020, complete genome</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>20A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>20A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>20A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B.1</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>B.1</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.694444</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -28052,46 +25241,46 @@
         </is>
       </c>
       <c r="K12" t="n">
+        <v>14</v>
+      </c>
+      <c r="L12" t="n">
+        <v>23</v>
+      </c>
+      <c r="M12" t="n">
+        <v>9</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
         <v>5</v>
       </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
         <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>89467</v>
+        <v>89403</v>
       </c>
       <c r="V12" t="n">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="W12" t="n">
-        <v>29836</v>
+        <v>29903</v>
       </c>
       <c r="X12" t="n">
-        <v>0.9975253319064976</v>
+        <v>0.9981941611209576</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -28103,24 +25292,36 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>C241T,C3037T,C14408T,C18814T,A23403G</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
+          <t>A6035G,C8782T,A16467G,C17747T,A17858G,C18060T,C21386T,C23185T,T28144C,T29867C,C29870A,A29893G,A29897G,A29898G</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>29837-29859</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>21384:TTC,29866:CCTCT,29903:A</t>
+        </is>
+      </c>
       <c r="AD12" t="inlineStr"/>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>ORF1b:P314L,S:D614G</t>
+          <t>ORF1a:S1924G,ORF1b:P1427L,ORF1b:Y1464C,ORF1b:S2640F,ORF8:L84S</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>ORF1b:2639:F</t>
+        </is>
+      </c>
       <c r="AH12" t="inlineStr"/>
       <c r="AI12" t="inlineStr"/>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>C18814T</t>
+          <t>A6035G,A16467G,C21386T,C23185T,T29867C,C29870A,A29893G,A29897G,A29898G</t>
         </is>
       </c>
       <c r="AK12" t="n">
@@ -28130,14 +25331,18 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AN12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="AO12" t="inlineStr"/>
       <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>ORF1a:S1924G,ORF1b:S2640F</t>
+        </is>
+      </c>
       <c r="AR12" t="n">
         <v>0</v>
       </c>
@@ -28145,37 +25350,53 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>NODE_0000764</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>C18814T</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
+          <t>A6035G,A16467G,C17747T,A17858G,C18060T,C21386T,C23185T,T29867C,C29870A,A29893G,A29897G,A29898G</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>29837-29859</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>ORF1a:S1924G,ORF1b:P1427L,ORF1b:Y1464C,ORF1b:S2640F</t>
+        </is>
+      </c>
       <c r="BA12" t="inlineStr"/>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>NODE_0000764</t>
+          <t>A.1</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>C18814T</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
+          <t>A6035G,A16467G,C21386T,C23185T,T29867C,C29870A,A29893G,A29897G,A29898G</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>29837-29859</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>ORF1a:S1924G,ORF1b:S2640F</t>
+        </is>
+      </c>
       <c r="BF12" t="inlineStr"/>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
@@ -28221,10 +25442,10 @@
         <v>24</v>
       </c>
       <c r="CB12" t="n">
-        <v>-7</v>
+        <v>2</v>
       </c>
       <c r="CC12" t="n">
-        <v>0</v>
+        <v>8.333333</v>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
@@ -28232,7 +25453,7 @@
         </is>
       </c>
       <c r="CE12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="CF12" t="inlineStr"/>
       <c r="CG12" t="n">
@@ -28284,11 +25505,11 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>MT159718.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/Cruise-CDC-03053369-001/2020, complete genome</t>
+          <t>MT159716.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/Cruise-CDC-03056442-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -28326,10 +25547,10 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -28347,7 +25568,7 @@
         <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -28356,7 +25577,7 @@
         <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>89634</v>
+        <v>89586</v>
       </c>
       <c r="V13" t="n">
         <v>1</v>
@@ -28377,43 +25598,51 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>G11083T,C28409T,G29736T</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr"/>
+          <t>G11083T,C22033A</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>509-523</t>
+        </is>
+      </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr"/>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>N:P46S,ORF1a:L3606F</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr"/>
+          <t>ORF1a:L3606F,S:F157L</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>ORF1a:G82-,ORF1a:H83-,ORF1a:V84-,ORF1a:M85-,ORF1a:V86-</t>
+        </is>
+      </c>
       <c r="AG13" t="inlineStr"/>
       <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>C28409T,G29736T</t>
-        </is>
-      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>C22033A|24A&amp;24E&amp;22D&amp;25C&amp;24C&amp;23C&amp;24F&amp;23F&amp;24B&amp;rec&amp;25B&amp;25A&amp;24G&amp;23I&amp;24H&amp;24D&amp;25D&amp;25G&amp;24I&amp;25E&amp;25H&amp;25F</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr"/>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AM13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO13" t="inlineStr"/>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>N:P46S</t>
+          <t>S:F157L</t>
         </is>
       </c>
       <c r="AR13" t="n">
@@ -28436,16 +25665,24 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>G11083T,C28409T,G29736T</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>G11083T,C22033A</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>509-523</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>N:P46S,ORF1a:L3606F</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
+          <t>ORF1a:L3606F,S:F157L</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>ORF1a:G82-,ORF1a:H83-,ORF1a:V84-,ORF1a:M85-,ORF1a:V86-</t>
+        </is>
+      </c>
       <c r="BB13" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
@@ -28453,16 +25690,24 @@
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>G11083T,C28409T,G29736T</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr"/>
+          <t>G11083T,C22033A</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>509-523</t>
+        </is>
+      </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>N:P46S,ORF1a:L3606F</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr"/>
+          <t>ORF1a:L3606F,S:F157L</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>ORF1a:G82-,ORF1a:H83-,ORF1a:V84-,ORF1a:M85-,ORF1a:V86-</t>
+        </is>
+      </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr"/>
@@ -28507,7 +25752,7 @@
         <v>24</v>
       </c>
       <c r="CB13" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
@@ -28518,7 +25763,7 @@
         </is>
       </c>
       <c r="CE13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="CF13" t="inlineStr"/>
       <c r="CG13" t="n">
@@ -28570,11 +25815,11 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MT163720.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA8-UW5/2020, complete genome</t>
+          <t>MT135044.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/235/2020, complete genome</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -28595,12 +25840,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -28612,7 +25857,7 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -28630,7 +25875,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -28642,16 +25887,16 @@
         <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>89164</v>
+        <v>89693</v>
       </c>
       <c r="V14" t="n">
-        <v>172</v>
+        <v>1</v>
       </c>
       <c r="W14" t="n">
         <v>29903</v>
       </c>
       <c r="X14" t="n">
-        <v>0.9942815102163662</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -28663,7 +25908,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>A3406C,C5784T,C8782T,C17747T,A17858G,C18060T,C23525T,T28144C</t>
+          <t>T4402C,G5062T,C8782T,T28144C</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr"/>
@@ -28671,39 +25916,35 @@
       <c r="AD14" t="inlineStr"/>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>ORF1a:E1047D,ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C,ORF8:L84S,S:H655Y</t>
+          <t>ORF1a:L1599F,ORF8:L84S</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="inlineStr"/>
       <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>C23525T|21K&amp;21L&amp;22B&amp;22E&amp;23A&amp;22C&amp;24A&amp;22A&amp;23F&amp;23D&amp;20J&amp;23B&amp;22D&amp;24E&amp;22F&amp;rec&amp;25C&amp;23C&amp;24C&amp;24F&amp;23E&amp;24B&amp;23H&amp;25B&amp;25A&amp;23I&amp;24G&amp;23G&amp;24H&amp;24D&amp;21M&amp;25D&amp;24I&amp;25G&amp;25E&amp;25I&amp;25H&amp;25F</t>
-        </is>
-      </c>
+      <c r="AI14" t="inlineStr"/>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>A3406C,C5784T</t>
+          <t>T4402C,G5062T</t>
         </is>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM14" t="n">
         <v>2</v>
       </c>
       <c r="AN14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="inlineStr"/>
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>ORF1a:E1047D,ORF1a:T1840I,S:H655Y</t>
+          <t>ORF1a:L1599F</t>
         </is>
       </c>
       <c r="AR14" t="n">
@@ -28713,10 +25954,10 @@
         <v>0</v>
       </c>
       <c r="AT14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -28726,30 +25967,30 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>A3406C,C5784T,C17747T,A17858G,C18060T,C23525T</t>
+          <t>T4402C,G5062T</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>ORF1a:E1047D,ORF1a:T1840I,ORF1b:P1427L,ORF1b:Y1464C,S:H655Y</t>
+          <t>ORF1a:L1599F</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr"/>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>A3406C,C5784T,C23525T</t>
+          <t>T4402C,G5062T</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr"/>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>ORF1a:E1047D,ORF1a:T1840I,S:H655Y</t>
+          <t>ORF1a:L1599F</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr"/>
@@ -28797,7 +26038,7 @@
         <v>24</v>
       </c>
       <c r="CB14" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="CC14" t="n">
         <v>0</v>
@@ -28808,7 +26049,7 @@
         </is>
       </c>
       <c r="CE14" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="CF14" t="inlineStr"/>
       <c r="CG14" t="n">
@@ -28860,11 +26101,11 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MT123290.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/IQTC01/2020, complete genome</t>
+          <t>MT159718.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/Cruise-CDC-03053369-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -28902,13 +26143,13 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -28920,7 +26161,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -28932,16 +26173,16 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>89636</v>
+        <v>89634</v>
       </c>
       <c r="V15" t="n">
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>29888</v>
+        <v>29882</v>
       </c>
       <c r="X15" t="n">
-        <v>0.999498378089155</v>
+        <v>0.9992977293248168</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -28953,19 +26194,15 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+          <t>G11083T,C28409T,G29736T</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr"/>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>0:GTT</t>
-        </is>
-      </c>
+      <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr"/>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>N:P344S</t>
+          <t>N:P46S,ORF1a:L3606F</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr"/>
@@ -28974,7 +26211,7 @@
       <c r="AI15" t="inlineStr"/>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+          <t>C28409T,G29736T</t>
         </is>
       </c>
       <c r="AK15" t="n">
@@ -28984,16 +26221,16 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AN15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AO15" t="inlineStr"/>
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>N:P344S</t>
+          <t>N:P46S</t>
         </is>
       </c>
       <c r="AR15" t="n">
@@ -29016,13 +26253,13 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+          <t>G11083T,C28409T,G29736T</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>N:P344S</t>
+          <t>N:P46S,ORF1a:L3606F</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr"/>
@@ -29033,13 +26270,13 @@
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+          <t>G11083T,C28409T,G29736T</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr"/>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>N:P344S</t>
+          <t>N:P46S,ORF1a:L3606F</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr"/>
@@ -29087,7 +26324,7 @@
         <v>24</v>
       </c>
       <c r="CB15" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="CC15" t="n">
         <v>0</v>
@@ -29098,7 +26335,7 @@
         </is>
       </c>
       <c r="CE15" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="CF15" t="inlineStr"/>
       <c r="CG15" t="n">
@@ -29150,37 +26387,37 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MT188341.1 Severe acute respiratory syndrome coronavirus 2 isolate USA/MN1-MDH1/2020, complete genome</t>
+          <t>MT163716.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA3-UW1/2020, complete genome</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -29192,13 +26429,13 @@
         </is>
       </c>
       <c r="K16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L16" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
@@ -29210,28 +26447,28 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>89403</v>
+        <v>89657</v>
       </c>
       <c r="V16" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="W16" t="n">
         <v>29903</v>
       </c>
       <c r="X16" t="n">
-        <v>0.9981941611209576</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -29243,36 +26480,24 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>A6035G,C8782T,A16467G,C17747T,A17858G,C18060T,C21386T,C23185T,T28144C,T29867C,C29870A,A29893G,A29897G,A29898G</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>29837-29859</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>21384:TTC,29866:CCTCT,29903:A</t>
-        </is>
-      </c>
+          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G11083T,C14805T,G26144T,G29864A,T29867A,G29868A,C29870A</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr"/>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>ORF1a:S1924G,ORF1b:P1427L,ORF1b:Y1464C,ORF1b:S2640F,ORF8:L84S</t>
+          <t>ORF1a:A1049V,ORF1a:M1769I,ORF1a:L3606F,ORF3a:G251V</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>ORF1b:2639:F</t>
-        </is>
-      </c>
+      <c r="AG16" t="inlineStr"/>
       <c r="AH16" t="inlineStr"/>
       <c r="AI16" t="inlineStr"/>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>A6035G,A16467G,C21386T,C23185T,T29867C,C29870A,A29893G,A29897G,A29898G</t>
+          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G29864A,T29867A,G29868A,C29870A</t>
         </is>
       </c>
       <c r="AK16" t="n">
@@ -29282,16 +26507,16 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AN16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="inlineStr"/>
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>ORF1a:S1924G,ORF1b:S2640F</t>
+          <t>ORF1a:A1049V,ORF1a:M1769I</t>
         </is>
       </c>
       <c r="AR16" t="n">
@@ -29309,43 +26534,35 @@
       <c r="AV16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>A6035G,A16467G,C17747T,A17858G,C18060T,C21386T,C23185T,T29867C,C29870A,A29893G,A29897G,A29898G</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>29837-29859</t>
-        </is>
-      </c>
+          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G11083T,C14805T,G26144T,G29864A,T29867A,G29868A,C29870A</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>ORF1a:S1924G,ORF1b:P1427L,ORF1b:Y1464C,ORF1b:S2640F</t>
+          <t>ORF1a:A1049V,ORF1a:M1769I,ORF1a:L3606F,ORF3a:G251V</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr"/>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>A.1</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>A6035G,A16467G,C21386T,C23185T,T29867C,C29870A,A29893G,A29897G,A29898G</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>29837-29859</t>
-        </is>
-      </c>
+          <t>A1T,A35T,C36T,T2446C,C3411T,G5572T,G11083T,C14805T,G26144T,G29864A,T29867A,G29868A,C29870A</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr"/>
       <c r="BE16" t="inlineStr">
         <is>
-          <t>ORF1a:S1924G,ORF1b:S2640F</t>
+          <t>ORF1a:A1049V,ORF1a:M1769I,ORF1a:L3606F,ORF3a:G251V</t>
         </is>
       </c>
       <c r="BF16" t="inlineStr"/>
@@ -29456,11 +26673,11 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MT159716.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/Cruise-CDC-03056442-001/2020, complete genome</t>
+          <t>MT123290.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/IQTC01/2020, complete genome</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -29498,13 +26715,13 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L17" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -29516,10 +26733,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -29528,16 +26745,16 @@
         <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>89586</v>
+        <v>89636</v>
       </c>
       <c r="V17" t="n">
         <v>1</v>
       </c>
       <c r="W17" t="n">
-        <v>29882</v>
+        <v>29888</v>
       </c>
       <c r="X17" t="n">
-        <v>0.9992977293248168</v>
+        <v>0.999498378089155</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -29549,51 +26766,47 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>G11083T,C22033A</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>509-523</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr"/>
+          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>0:GTT</t>
+        </is>
+      </c>
       <c r="AD17" t="inlineStr"/>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,S:F157L</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>ORF1a:G82-,ORF1a:H83-,ORF1a:V84-,ORF1a:M85-,ORF1a:V86-</t>
-        </is>
-      </c>
+          <t>N:P344S</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="inlineStr"/>
       <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>C22033A|24A&amp;24E&amp;22D&amp;25C&amp;24C&amp;23C&amp;24F&amp;23F&amp;24B&amp;rec&amp;25B&amp;25A&amp;24G&amp;23I&amp;24H&amp;24D&amp;25D&amp;25G&amp;24I&amp;25E&amp;25H&amp;25F</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+        </is>
+      </c>
       <c r="AK17" t="n">
         <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AN17" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AO17" t="inlineStr"/>
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>S:F157L</t>
+          <t>N:P344S</t>
         </is>
       </c>
       <c r="AR17" t="n">
@@ -29616,24 +26829,16 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>G11083T,C22033A</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>509-523</t>
-        </is>
-      </c>
+          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,S:F157L</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>ORF1a:G82-,ORF1a:H83-,ORF1a:V84-,ORF1a:M85-,ORF1a:V86-</t>
-        </is>
-      </c>
+          <t>N:P344S</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr"/>
       <c r="BB17" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
@@ -29641,24 +26846,16 @@
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>G11083T,C22033A</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>509-523</t>
-        </is>
-      </c>
+          <t>A1C,A4T,C15324T,C29303T,A29884G,A29885G,A29887G</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr"/>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,S:F157L</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>ORF1a:G82-,ORF1a:H83-,ORF1a:V84-,ORF1a:M85-,ORF1a:V86-</t>
-        </is>
-      </c>
+          <t>N:P344S</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr"/>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr"/>
@@ -29703,7 +26900,7 @@
         <v>24</v>
       </c>
       <c r="CB17" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="CC17" t="n">
         <v>0</v>
@@ -29714,7 +26911,7 @@
         </is>
       </c>
       <c r="CE17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="CF17" t="inlineStr"/>
       <c r="CG17" t="n">
@@ -30060,11 +27257,11 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MT093631.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/WH-09/2020, complete genome</t>
+          <t>MT066156.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/ITA/INMI1/2020, complete genome</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -30102,7 +27299,7 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -30114,13 +27311,13 @@
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" t="n">
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -30129,23 +27326,23 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U19" t="n">
-        <v>89576</v>
+        <v>89592</v>
       </c>
       <c r="V19" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>29873</v>
+        <v>29867</v>
       </c>
       <c r="X19" t="n">
-        <v>0.9985620171889108</v>
+        <v>0.9987626659532488</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>E:1,M:1,N:1,ORF1a:1,ORF1b:1,ORF3a:1,ORF6:1,ORF7a:1,ORF7b:1,ORF8:1,ORF9b:1,S:1</t>
+          <t>E:1,M:1,N:1,ORF1a:0.9997727789138832,ORF1b:1,ORF3a:1,ORF6:1,ORF7a:1,ORF7b:1,ORF8:1,ORF9b:1,S:1</t>
         </is>
       </c>
       <c r="Z19" t="b">
@@ -30153,24 +27350,32 @@
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>C186T</t>
+          <t>A2269T,G26144T</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>ORF3a:G251V</t>
+        </is>
+      </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>T14805C</t>
+        </is>
+      </c>
       <c r="AI19" t="inlineStr"/>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>C186T</t>
+          <t>A2269T</t>
         </is>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
@@ -30179,7 +27384,7 @@
         <v>1</v>
       </c>
       <c r="AN19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO19" t="inlineStr"/>
       <c r="AP19" t="inlineStr"/>
@@ -30196,7 +27401,9 @@
       <c r="AU19" t="n">
         <v>0</v>
       </c>
-      <c r="AV19" t="inlineStr"/>
+      <c r="AV19" t="n">
+        <v>11083</v>
+      </c>
       <c r="AW19" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
@@ -30204,11 +27411,15 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>C186T</t>
+          <t>A2269T,G26144T</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>ORF3a:G251V</t>
+        </is>
+      </c>
       <c r="BA19" t="inlineStr"/>
       <c r="BB19" t="inlineStr">
         <is>
@@ -30217,11 +27428,15 @@
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>C186T</t>
+          <t>A2269T,G26144T</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>ORF3a:G251V</t>
+        </is>
+      </c>
       <c r="BF19" t="inlineStr"/>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
@@ -30233,7 +27448,11 @@
       <c r="BN19" t="inlineStr"/>
       <c r="BO19" t="inlineStr"/>
       <c r="BP19" t="inlineStr"/>
-      <c r="BQ19" t="inlineStr"/>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>ORF1a:3606</t>
+        </is>
+      </c>
       <c r="BR19" t="inlineStr"/>
       <c r="BS19" t="n">
         <v>3000</v>
@@ -30247,7 +27466,7 @@
         </is>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BW19" t="n">
         <v>10</v>
@@ -30267,7 +27486,7 @@
         <v>24</v>
       </c>
       <c r="CB19" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="CC19" t="n">
         <v>0</v>
@@ -30278,7 +27497,7 @@
         </is>
       </c>
       <c r="CE19" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="CF19" t="inlineStr"/>
       <c r="CG19" t="n">
@@ -30330,37 +27549,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MT093571.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/SWE/01/2020, complete genome</t>
+          <t>MT066175.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/NTU01/TWN/human/2020, complete genome</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -30372,7 +27591,7 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -30390,7 +27609,7 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -30402,16 +27621,16 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>89630</v>
+        <v>89602</v>
       </c>
       <c r="V20" t="n">
         <v>1</v>
       </c>
       <c r="W20" t="n">
-        <v>29886</v>
+        <v>29870</v>
       </c>
       <c r="X20" t="n">
-        <v>0.9994314951677088</v>
+        <v>0.9988964317961408</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -30423,7 +27642,7 @@
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
+          <t>C8782T,T28144C</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr"/>
@@ -30431,18 +27650,14 @@
       <c r="AD20" t="inlineStr"/>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
+          <t>ORF8:L84S</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="inlineStr"/>
       <c r="AH20" t="inlineStr"/>
       <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
-        </is>
-      </c>
+      <c r="AJ20" t="inlineStr"/>
       <c r="AK20" t="n">
         <v>0</v>
       </c>
@@ -30450,18 +27665,14 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="inlineStr"/>
       <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
-        </is>
-      </c>
+      <c r="AQ20" t="inlineStr"/>
       <c r="AR20" t="n">
         <v>0</v>
       </c>
@@ -30469,45 +27680,29 @@
         <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
-        </is>
-      </c>
+          <t>internal_b384</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr"/>
       <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
-        </is>
-      </c>
+      <c r="AZ20" t="inlineStr"/>
       <c r="BA20" t="inlineStr"/>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
-        </is>
-      </c>
+          <t>internal_b384</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr"/>
       <c r="BD20" t="inlineStr"/>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
-        </is>
-      </c>
+      <c r="BE20" t="inlineStr"/>
       <c r="BF20" t="inlineStr"/>
       <c r="BG20" t="inlineStr"/>
       <c r="BH20" t="inlineStr"/>
@@ -30553,7 +27748,7 @@
         <v>24</v>
       </c>
       <c r="CB20" t="n">
-        <v>-1</v>
+        <v>-8</v>
       </c>
       <c r="CC20" t="n">
         <v>0</v>
@@ -30564,7 +27759,7 @@
         </is>
       </c>
       <c r="CE20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="CF20" t="inlineStr"/>
       <c r="CG20" t="n">
@@ -30616,37 +27811,37 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MT072688.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/NPL/61-TW/2020, complete genome</t>
+          <t>MT050493.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/IND/166/2020, complete genome</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -30658,7 +27853,7 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -30676,7 +27871,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -30688,16 +27883,16 @@
         <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>89429</v>
+        <v>89529</v>
       </c>
       <c r="V21" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="W21" t="n">
-        <v>29826</v>
+        <v>29871</v>
       </c>
       <c r="X21" t="n">
-        <v>0.9969233856134836</v>
+        <v>0.9982610440424038</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -30709,20 +27904,24 @@
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>C24034T</t>
+          <t>A1691G,C6501T,C8782T,C16877T,C24351T,T28144C</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr"/>
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,ORF8:L84S,S:A930V</t>
+        </is>
+      </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="inlineStr"/>
       <c r="AH21" t="inlineStr"/>
       <c r="AI21" t="inlineStr"/>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>C24034T</t>
+          <t>A1691G,C6501T,C16877T,C24351T</t>
         </is>
       </c>
       <c r="AK21" t="n">
@@ -30732,14 +27931,18 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AN21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AO21" t="inlineStr"/>
       <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,S:A930V</t>
+        </is>
+      </c>
       <c r="AR21" t="n">
         <v>0</v>
       </c>
@@ -30747,37 +27950,45 @@
         <v>0</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AV21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>C24034T</t>
+          <t>A1691G,C6501T,C16877T,C24351T</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,S:A930V</t>
+        </is>
+      </c>
       <c r="BA21" t="inlineStr"/>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>C24034T</t>
+          <t>A1691G,C6501T,C16877T,C24351T</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr"/>
-      <c r="BE21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,S:A930V</t>
+        </is>
+      </c>
       <c r="BF21" t="inlineStr"/>
       <c r="BG21" t="inlineStr"/>
       <c r="BH21" t="inlineStr"/>
@@ -30823,7 +28034,7 @@
         <v>24</v>
       </c>
       <c r="CB21" t="n">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="CC21" t="n">
         <v>0</v>
@@ -30834,7 +28045,7 @@
         </is>
       </c>
       <c r="CE21" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CF21" t="inlineStr"/>
       <c r="CG21" t="n">
@@ -30886,37 +28097,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MT066175.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/NTU01/TWN/human/2020, complete genome</t>
+          <t>MT072688.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/NPL/61-TW/2020, complete genome</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -30928,7 +28139,7 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -30946,7 +28157,7 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -30958,16 +28169,16 @@
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>89602</v>
+        <v>89429</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="W22" t="n">
-        <v>29870</v>
+        <v>29826</v>
       </c>
       <c r="X22" t="n">
-        <v>0.9988964317961408</v>
+        <v>0.9969233856134836</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -30979,22 +28190,22 @@
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>C8782T,T28144C</t>
+          <t>C24034T</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>ORF8:L84S</t>
-        </is>
-      </c>
+      <c r="AE22" t="inlineStr"/>
       <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="inlineStr"/>
       <c r="AH22" t="inlineStr"/>
       <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>C24034T</t>
+        </is>
+      </c>
       <c r="AK22" t="n">
         <v>0</v>
       </c>
@@ -31002,10 +28213,10 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO22" t="inlineStr"/>
       <c r="AP22" t="inlineStr"/>
@@ -31025,19 +28236,27 @@
       <c r="AV22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>internal_b384</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>NODE_0000000</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>C24034T</t>
+        </is>
+      </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr"/>
       <c r="BA22" t="inlineStr"/>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>internal_b384</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr"/>
+          <t>NODE_0000000</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>C24034T</t>
+        </is>
+      </c>
       <c r="BD22" t="inlineStr"/>
       <c r="BE22" t="inlineStr"/>
       <c r="BF22" t="inlineStr"/>
@@ -31085,7 +28304,7 @@
         <v>24</v>
       </c>
       <c r="CB22" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="CC22" t="n">
         <v>0</v>
@@ -31096,7 +28315,7 @@
         </is>
       </c>
       <c r="CE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF22" t="inlineStr"/>
       <c r="CG22" t="n">
@@ -31148,37 +28367,37 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MN997409.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/AZ-CDC-02993465-001/2020, complete genome</t>
+          <t>MT093631.2 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/WH-09/2020, complete genome</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -31190,7 +28409,7 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -31208,7 +28427,7 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -31220,16 +28439,16 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>89630</v>
+        <v>89576</v>
       </c>
       <c r="V23" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="W23" t="n">
-        <v>29882</v>
+        <v>29873</v>
       </c>
       <c r="X23" t="n">
-        <v>0.9992977293248168</v>
+        <v>0.9985620171889108</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -31241,24 +28460,20 @@
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>C8782T,G11083T,T28144C,C29095T</t>
+          <t>C186T</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>ORF1a:L3606F,ORF8:L84S</t>
-        </is>
-      </c>
+      <c r="AE23" t="inlineStr"/>
       <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="inlineStr"/>
       <c r="AH23" t="inlineStr"/>
       <c r="AI23" t="inlineStr"/>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>G11083T,C29095T</t>
+          <t>C186T</t>
         </is>
       </c>
       <c r="AK23" t="n">
@@ -31268,18 +28483,14 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO23" t="inlineStr"/>
       <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>ORF1a:L3606F</t>
-        </is>
-      </c>
+      <c r="AQ23" t="inlineStr"/>
       <c r="AR23" t="n">
         <v>0</v>
       </c>
@@ -31287,45 +28498,37 @@
         <v>0</v>
       </c>
       <c r="AT23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>G11083T,C29095T</t>
+          <t>C186T</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>ORF1a:L3606F</t>
-        </is>
-      </c>
+      <c r="AZ23" t="inlineStr"/>
       <c r="BA23" t="inlineStr"/>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>G11083T,C29095T</t>
+          <t>C186T</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr"/>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>ORF1a:L3606F</t>
-        </is>
-      </c>
+      <c r="BE23" t="inlineStr"/>
       <c r="BF23" t="inlineStr"/>
       <c r="BG23" t="inlineStr"/>
       <c r="BH23" t="inlineStr"/>
@@ -31371,7 +28574,7 @@
         <v>24</v>
       </c>
       <c r="CB23" t="n">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="CC23" t="n">
         <v>0</v>
@@ -31382,7 +28585,7 @@
         </is>
       </c>
       <c r="CE23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CF23" t="inlineStr"/>
       <c r="CG23" t="n">
@@ -31434,37 +28637,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MT050493.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/IND/166/2020, complete genome</t>
+          <t>MT039887.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WI-CDC-03041142-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -31476,10 +28679,10 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M24" t="n">
         <v>0</v>
@@ -31494,10 +28697,10 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -31506,16 +28709,16 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>89529</v>
+        <v>89626</v>
       </c>
       <c r="V24" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>29871</v>
+        <v>29882</v>
       </c>
       <c r="X24" t="n">
-        <v>0.9982610440424038</v>
+        <v>0.9992977293248168</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -31527,24 +28730,28 @@
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>A1691G,C6501T,C8782T,C16877T,C24351T,T28144C</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr"/>
+          <t>C17373T</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>20299-20301</t>
+        </is>
+      </c>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,ORF8:L84S,S:A930V</t>
-        </is>
-      </c>
-      <c r="AF24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>ORF1b:L2278-</t>
+        </is>
+      </c>
       <c r="AG24" t="inlineStr"/>
       <c r="AH24" t="inlineStr"/>
       <c r="AI24" t="inlineStr"/>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>A1691G,C6501T,C16877T,C24351T</t>
+          <t>C17373T</t>
         </is>
       </c>
       <c r="AK24" t="n">
@@ -31554,18 +28761,14 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AN24" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AO24" t="inlineStr"/>
       <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr">
-        <is>
-          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,S:A930V</t>
-        </is>
-      </c>
+      <c r="AQ24" t="inlineStr"/>
       <c r="AR24" t="n">
         <v>0</v>
       </c>
@@ -31573,46 +28776,54 @@
         <v>0</v>
       </c>
       <c r="AT24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AU24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AV24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>A1691G,C6501T,C16877T,C24351T</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,S:A930V</t>
-        </is>
-      </c>
-      <c r="BA24" t="inlineStr"/>
+          <t>C17373T</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>20299-20301</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr"/>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>ORF1b:L2278-</t>
+        </is>
+      </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>A1691G,C6501T,C16877T,C24351T</t>
-        </is>
-      </c>
-      <c r="BD24" t="inlineStr"/>
-      <c r="BE24" t="inlineStr">
-        <is>
-          <t>ORF1a:I476V,ORF1a:P2079L,ORF1b:T1137I,S:A930V</t>
-        </is>
-      </c>
-      <c r="BF24" t="inlineStr"/>
+          <t>C17373T</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>20299-20301</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr"/>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>ORF1b:L2278-</t>
+        </is>
+      </c>
       <c r="BG24" t="inlineStr"/>
       <c r="BH24" t="inlineStr"/>
       <c r="BI24" t="inlineStr"/>
@@ -31657,7 +28868,7 @@
         <v>24</v>
       </c>
       <c r="CB24" t="n">
-        <v>-4</v>
+        <v>-6</v>
       </c>
       <c r="CC24" t="n">
         <v>0</v>
@@ -31668,7 +28879,7 @@
         </is>
       </c>
       <c r="CE24" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="CF24" t="inlineStr"/>
       <c r="CG24" t="n">
@@ -31720,37 +28931,37 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MT049951.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/Yunnan-01/2020, complete genome</t>
+          <t>MT093571.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/SWE/01/2020, complete genome</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -31762,7 +28973,7 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -31780,7 +28991,7 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -31792,16 +29003,16 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>89689</v>
+        <v>89630</v>
       </c>
       <c r="V25" t="n">
         <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>29903</v>
+        <v>29886</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>0.9994314951677088</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
@@ -31813,7 +29024,7 @@
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>C75A,C8782T,G11083C,T21644A,T28144C</t>
+          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -31821,7 +29032,7 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,ORF8:L84S,S:Y28N</t>
+          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr"/>
@@ -31830,7 +29041,7 @@
       <c r="AI25" t="inlineStr"/>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>C75A,G11083C,T21644A</t>
+          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
         </is>
       </c>
       <c r="AK25" t="n">
@@ -31840,16 +29051,16 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AN25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AO25" t="inlineStr"/>
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,S:Y28N</t>
+          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
         </is>
       </c>
       <c r="AR25" t="n">
@@ -31859,43 +29070,43 @@
         <v>0</v>
       </c>
       <c r="AT25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AU25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>C75A,G11083C,T21644A</t>
+          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,S:Y28N</t>
+          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
         </is>
       </c>
       <c r="BA25" t="inlineStr"/>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>C75A,G11083C,T21644A</t>
+          <t>G2717A,A9274G,C13225G,T13226C,A17376G,T23952G,G26144T</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr"/>
       <c r="BE25" t="inlineStr">
         <is>
-          <t>ORF1a:L3606F,S:Y28N</t>
+          <t>ORF1a:G818S,ORF1a:F4321L,ORF3a:G251V,S:F797C</t>
         </is>
       </c>
       <c r="BF25" t="inlineStr"/>
@@ -31943,7 +29154,7 @@
         <v>24</v>
       </c>
       <c r="CB25" t="n">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="CC25" t="n">
         <v>0</v>
@@ -31954,7 +29165,7 @@
         </is>
       </c>
       <c r="CE25" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CF25" t="inlineStr"/>
       <c r="CG25" t="n">
@@ -32006,37 +29217,37 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MT039873.1 Severe acute respiratory syndrome coronavirus 2 isolate HZ-1, complete genome</t>
+          <t>MT049951.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/CHN/Yunnan-01/2020, complete genome</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -32048,7 +29259,7 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -32066,7 +29277,7 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -32078,16 +29289,16 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>89499</v>
+        <v>89689</v>
       </c>
       <c r="V26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>29836</v>
+        <v>29903</v>
       </c>
       <c r="X26" t="n">
-        <v>0.9976590977493895</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
@@ -32097,16 +29308,28 @@
       <c r="Z26" t="b">
         <v>0</v>
       </c>
-      <c r="AA26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>C75A,C8782T,G11083C,T21644A,T28144C</t>
+        </is>
+      </c>
       <c r="AB26" t="inlineStr"/>
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F,ORF8:L84S,S:Y28N</t>
+        </is>
+      </c>
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
       <c r="AH26" t="inlineStr"/>
       <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>C75A,G11083C,T21644A</t>
+        </is>
+      </c>
       <c r="AK26" t="n">
         <v>0</v>
       </c>
@@ -32114,14 +29337,18 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO26" t="inlineStr"/>
       <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F,S:Y28N</t>
+        </is>
+      </c>
       <c r="AR26" t="n">
         <v>0</v>
       </c>
@@ -32129,29 +29356,45 @@
         <v>0</v>
       </c>
       <c r="AT26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>internal_b384</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>C75A,G11083C,T21644A</t>
+        </is>
+      </c>
       <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F,S:Y28N</t>
+        </is>
+      </c>
       <c r="BA26" t="inlineStr"/>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
-        </is>
-      </c>
-      <c r="BC26" t="inlineStr"/>
+          <t>internal_b384</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>C75A,G11083C,T21644A</t>
+        </is>
+      </c>
       <c r="BD26" t="inlineStr"/>
-      <c r="BE26" t="inlineStr"/>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F,S:Y28N</t>
+        </is>
+      </c>
       <c r="BF26" t="inlineStr"/>
       <c r="BG26" t="inlineStr"/>
       <c r="BH26" t="inlineStr"/>
@@ -32197,7 +29440,7 @@
         <v>24</v>
       </c>
       <c r="CB26" t="n">
-        <v>-8</v>
+        <v>-5</v>
       </c>
       <c r="CC26" t="n">
         <v>0</v>
@@ -32208,7 +29451,7 @@
         </is>
       </c>
       <c r="CE26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="CF26" t="inlineStr"/>
       <c r="CG26" t="n">
@@ -32260,11 +29503,11 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MT020781.2 Severe acute respiratory syndrome coronavirus 2 isolate nCoV-FIN-29-Jan-2020, complete genome</t>
+          <t>MT039890.1 Severe acute respiratory syndrome coronavirus 2 isolate SNU01, complete genome</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -32294,7 +29537,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.173611</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -32302,7 +29545,7 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -32320,7 +29563,7 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -32332,16 +29575,16 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>89410</v>
+        <v>89673</v>
       </c>
       <c r="V27" t="n">
         <v>1</v>
       </c>
       <c r="W27" t="n">
-        <v>29806</v>
+        <v>29903</v>
       </c>
       <c r="X27" t="n">
-        <v>0.9967561783098686</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
@@ -32353,7 +29596,7 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>A1C,C21707T</t>
+          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -32361,7 +29604,7 @@
       <c r="AD27" t="inlineStr"/>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>S:H49Y</t>
+          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr"/>
@@ -32370,7 +29613,7 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>A1C,C21707T</t>
+          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
         </is>
       </c>
       <c r="AK27" t="n">
@@ -32380,16 +29623,16 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AN27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="AO27" t="inlineStr"/>
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>S:H49Y</t>
+          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
         </is>
       </c>
       <c r="AR27" t="n">
@@ -32399,10 +29642,10 @@
         <v>0</v>
       </c>
       <c r="AT27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AU27" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="AV27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -32412,13 +29655,13 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>A1C,C21707T</t>
+          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>S:H49Y</t>
+          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
         </is>
       </c>
       <c r="BA27" t="inlineStr"/>
@@ -32429,13 +29672,13 @@
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>A1C,C21707T</t>
+          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr"/>
       <c r="BE27" t="inlineStr">
         <is>
-          <t>S:H49Y</t>
+          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
         </is>
       </c>
       <c r="BF27" t="inlineStr"/>
@@ -32483,10 +29726,10 @@
         <v>24</v>
       </c>
       <c r="CB27" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
       <c r="CC27" t="n">
-        <v>0</v>
+        <v>4.166667</v>
       </c>
       <c r="CD27" t="inlineStr">
         <is>
@@ -32494,7 +29737,7 @@
         </is>
       </c>
       <c r="CE27" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="CF27" t="inlineStr"/>
       <c r="CG27" t="n">
@@ -32546,52 +29789,52 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MT044257.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/IL-CDC-03037667-001/2020, complete genome</t>
+          <t>MT007544.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/AUS/VIC01/2020, complete genome</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>A.3</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>A.3</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>84.027778</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>mediocre</t>
+          <t>good</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -32606,7 +29849,7 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -32618,16 +29861,16 @@
         <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>89618</v>
+        <v>89661</v>
       </c>
       <c r="V28" t="n">
         <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>29882</v>
+        <v>29903</v>
       </c>
       <c r="X28" t="n">
-        <v>0.9992977293248168</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
@@ -32639,89 +29882,101 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>T490A,C3177T,C8782T,C24034T,T26729C,G28077C,T28144C</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr"/>
+          <t>T19065C,T22303G,G26144T</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>29750-29759</t>
+        </is>
+      </c>
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr"/>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>ORF1a:D75E,ORF1a:P971L,ORF8:V62L,ORF8:L84S</t>
+          <t>ORF3a:G251V,S:S247R</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>T6040C,A12478G,C18736T,G28896C,G29700A</t>
-        </is>
-      </c>
+      <c r="AH28" t="inlineStr"/>
       <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>T19065C,T22303G,G26144T</t>
+        </is>
+      </c>
       <c r="AK28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AL28" t="n">
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN28" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>N:G208A,ORF1a:I4071M,ORF1b:L1757F</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AO28" t="inlineStr"/>
       <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr">
+        <is>
+          <t>ORF3a:G251V,S:S247R</t>
+        </is>
+      </c>
       <c r="AR28" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AS28" t="n">
         <v>0</v>
       </c>
       <c r="AT28" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>T490A,C3177T,C24034T,T26729C,G28077C</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
+          <t>T19065C,T22303G,G26144T</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>29750-29759</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>ORF1a:D75E,ORF1a:P971L,ORF8:V62L</t>
+          <t>ORF3a:G251V,S:S247R</t>
         </is>
       </c>
       <c r="BA28" t="inlineStr"/>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>A.3</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>T6040C,A12478G,C18736T,G28896C,G29700A</t>
-        </is>
-      </c>
-      <c r="BD28" t="inlineStr"/>
+          <t>T19065C,T22303G,G26144T</t>
+        </is>
+      </c>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>29750-29759</t>
+        </is>
+      </c>
       <c r="BE28" t="inlineStr">
         <is>
-          <t>N:G208A,ORF1a:I4071M,ORF1b:L1757F</t>
+          <t>ORF3a:G251V,S:S247R</t>
         </is>
       </c>
       <c r="BF28" t="inlineStr"/>
@@ -32769,18 +30024,18 @@
         <v>24</v>
       </c>
       <c r="CB28" t="n">
-        <v>22</v>
+        <v>-4</v>
       </c>
       <c r="CC28" t="n">
-        <v>91.666667</v>
+        <v>0</v>
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>mediocre</t>
+          <t>good</t>
         </is>
       </c>
       <c r="CE28" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="CF28" t="inlineStr"/>
       <c r="CG28" t="n">
@@ -32832,11 +30087,11 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MT039887.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WI-CDC-03041142-001/2020, complete genome</t>
+          <t>MT020781.2 Severe acute respiratory syndrome coronavirus 2 isolate nCoV-FIN-29-Jan-2020, complete genome</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -32874,10 +30129,10 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -32892,10 +30147,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -32904,16 +30159,16 @@
         <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>89626</v>
+        <v>89410</v>
       </c>
       <c r="V29" t="n">
         <v>1</v>
       </c>
       <c r="W29" t="n">
-        <v>29882</v>
+        <v>29806</v>
       </c>
       <c r="X29" t="n">
-        <v>0.9992977293248168</v>
+        <v>0.9967561783098686</v>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
@@ -32925,28 +30180,24 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>C17373T</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>20299-20301</t>
-        </is>
-      </c>
+          <t>A1C,C21707T</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>ORF1b:L2278-</t>
-        </is>
-      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>S:H49Y</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="inlineStr"/>
       <c r="AH29" t="inlineStr"/>
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>C17373T</t>
+          <t>A1C,C21707T</t>
         </is>
       </c>
       <c r="AK29" t="n">
@@ -32956,14 +30207,18 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO29" t="inlineStr"/>
       <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr">
+        <is>
+          <t>S:H49Y</t>
+        </is>
+      </c>
       <c r="AR29" t="n">
         <v>0</v>
       </c>
@@ -32971,10 +30226,10 @@
         <v>0</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -32984,20 +30239,16 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>C17373T</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr">
-        <is>
-          <t>20299-20301</t>
-        </is>
-      </c>
-      <c r="AZ29" t="inlineStr"/>
-      <c r="BA29" t="inlineStr">
-        <is>
-          <t>ORF1b:L2278-</t>
-        </is>
-      </c>
+          <t>A1C,C21707T</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>S:H49Y</t>
+        </is>
+      </c>
+      <c r="BA29" t="inlineStr"/>
       <c r="BB29" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
@@ -33005,20 +30256,16 @@
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>C17373T</t>
-        </is>
-      </c>
-      <c r="BD29" t="inlineStr">
-        <is>
-          <t>20299-20301</t>
-        </is>
-      </c>
-      <c r="BE29" t="inlineStr"/>
-      <c r="BF29" t="inlineStr">
-        <is>
-          <t>ORF1b:L2278-</t>
-        </is>
-      </c>
+          <t>A1C,C21707T</t>
+        </is>
+      </c>
+      <c r="BD29" t="inlineStr"/>
+      <c r="BE29" t="inlineStr">
+        <is>
+          <t>S:H49Y</t>
+        </is>
+      </c>
+      <c r="BF29" t="inlineStr"/>
       <c r="BG29" t="inlineStr"/>
       <c r="BH29" t="inlineStr"/>
       <c r="BI29" t="inlineStr"/>
@@ -33126,11 +30373,11 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>MT007544.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/AUS/VIC01/2020, complete genome</t>
+          <t>MT039873.1 Severe acute respiratory syndrome coronavirus 2 isolate HZ-1, complete genome</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -33168,10 +30415,10 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -33186,7 +30433,7 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -33198,16 +30445,16 @@
         <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>89661</v>
+        <v>89499</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W30" t="n">
-        <v>29903</v>
+        <v>29836</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>0.9976590977493895</v>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
@@ -33217,32 +30464,16 @@
       <c r="Z30" t="b">
         <v>0</v>
       </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>T19065C,T22303G,G26144T</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>29750-29759</t>
-        </is>
-      </c>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr">
-        <is>
-          <t>ORF3a:G251V,S:S247R</t>
-        </is>
-      </c>
+      <c r="AE30" t="inlineStr"/>
       <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="inlineStr"/>
       <c r="AH30" t="inlineStr"/>
       <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>T19065C,T22303G,G26144T</t>
-        </is>
-      </c>
+      <c r="AJ30" t="inlineStr"/>
       <c r="AK30" t="n">
         <v>0</v>
       </c>
@@ -33250,18 +30481,14 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO30" t="inlineStr"/>
       <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr">
-        <is>
-          <t>ORF3a:G251V,S:S247R</t>
-        </is>
-      </c>
+      <c r="AQ30" t="inlineStr"/>
       <c r="AR30" t="n">
         <v>0</v>
       </c>
@@ -33269,10 +30496,10 @@
         <v>0</v>
       </c>
       <c r="AT30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -33280,42 +30507,18 @@
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>T19065C,T22303G,G26144T</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr">
-        <is>
-          <t>29750-29759</t>
-        </is>
-      </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>ORF3a:G251V,S:S247R</t>
-        </is>
-      </c>
+      <c r="AX30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr"/>
       <c r="BA30" t="inlineStr"/>
       <c r="BB30" t="inlineStr">
         <is>
           <t>NODE_0000000</t>
         </is>
       </c>
-      <c r="BC30" t="inlineStr">
-        <is>
-          <t>T19065C,T22303G,G26144T</t>
-        </is>
-      </c>
-      <c r="BD30" t="inlineStr">
-        <is>
-          <t>29750-29759</t>
-        </is>
-      </c>
-      <c r="BE30" t="inlineStr">
-        <is>
-          <t>ORF3a:G251V,S:S247R</t>
-        </is>
-      </c>
+      <c r="BC30" t="inlineStr"/>
+      <c r="BD30" t="inlineStr"/>
+      <c r="BE30" t="inlineStr"/>
       <c r="BF30" t="inlineStr"/>
       <c r="BG30" t="inlineStr"/>
       <c r="BH30" t="inlineStr"/>
@@ -33361,7 +30564,7 @@
         <v>24</v>
       </c>
       <c r="CB30" t="n">
-        <v>-4</v>
+        <v>-8</v>
       </c>
       <c r="CC30" t="n">
         <v>0</v>
@@ -33372,7 +30575,7 @@
         </is>
       </c>
       <c r="CE30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="CF30" t="inlineStr"/>
       <c r="CG30" t="n">
@@ -33424,49 +30627,49 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MT039890.1 Severe acute respiratory syndrome coronavirus 2 isolate SNU01, complete genome</t>
+          <t>MT044257.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/IL-CDC-03037667-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A.3</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A.3</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.173611</v>
+        <v>84.027778</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>mediocre</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -33484,7 +30687,7 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -33496,16 +30699,16 @@
         <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>89673</v>
+        <v>89618</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>29903</v>
+        <v>29882</v>
       </c>
       <c r="X31" t="n">
-        <v>1</v>
+        <v>0.9992977293248168</v>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
@@ -33517,7 +30720,7 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
+          <t>T490A,C3177T,C8782T,C24034T,T26729C,G28077C,T28144C</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr"/>
@@ -33525,81 +30728,81 @@
       <c r="AD31" t="inlineStr"/>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
+          <t>ORF1a:D75E,ORF1a:P971L,ORF8:V62L,ORF8:L84S</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>T6040C,A12478G,C18736T,G28896C,G29700A</t>
+        </is>
+      </c>
       <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
-        </is>
-      </c>
+      <c r="AJ31" t="inlineStr"/>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AL31" t="n">
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>9</v>
-      </c>
-      <c r="AO31" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>N:G208A,ORF1a:I4071M,ORF1b:L1757F</t>
+        </is>
+      </c>
       <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr">
-        <is>
-          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
-        </is>
-      </c>
+      <c r="AQ31" t="inlineStr"/>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AS31" t="n">
         <v>0</v>
       </c>
       <c r="AT31" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AU31" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AV31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
+          <t>T490A,C3177T,C24034T,T26729C,G28077C</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
+          <t>ORF1a:D75E,ORF1a:P971L,ORF8:V62L</t>
         </is>
       </c>
       <c r="BA31" t="inlineStr"/>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>A.3</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>G2971T,C6031T,C12115T,T15597C,C20936T,C22224G,G25775T,G26144T,T26354A</t>
+          <t>T6040C,A12478G,C18736T,G28896C,G29700A</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr"/>
       <c r="BE31" t="inlineStr">
         <is>
-          <t>E:L37H,ORF1a:M902I,ORF1b:T2490M,ORF3a:W128L,ORF3a:G251V,S:S221W</t>
+          <t>N:G208A,ORF1a:I4071M,ORF1b:L1757F</t>
         </is>
       </c>
       <c r="BF31" t="inlineStr"/>
@@ -33647,18 +30850,18 @@
         <v>24</v>
       </c>
       <c r="CB31" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="CC31" t="n">
-        <v>4.166667</v>
+        <v>91.666667</v>
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>mediocre</t>
         </is>
       </c>
       <c r="CE31" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="CF31" t="inlineStr"/>
       <c r="CG31" t="n">
@@ -34020,37 +31223,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MT066156.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/ITA/INMI1/2020, complete genome</t>
+          <t>MN997409.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/AZ-CDC-02993465-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -34062,26 +31265,26 @@
         </is>
       </c>
       <c r="K33" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>2</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>1</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>1</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -34089,23 +31292,23 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U33" t="n">
-        <v>89592</v>
+        <v>89630</v>
       </c>
       <c r="V33" t="n">
         <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>29867</v>
+        <v>29882</v>
       </c>
       <c r="X33" t="n">
-        <v>0.9987626659532488</v>
+        <v>0.9992977293248168</v>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>E:1,M:1,N:1,ORF1a:0.9997727789138832,ORF1b:1,ORF3a:1,ORF6:1,ORF7a:1,ORF7b:1,ORF8:1,ORF9b:1,S:1</t>
+          <t>E:1,M:1,N:1,ORF1a:1,ORF1b:1,ORF3a:1,ORF6:1,ORF7a:1,ORF7b:1,ORF8:1,ORF9b:1,S:1</t>
         </is>
       </c>
       <c r="Z33" t="b">
@@ -34113,7 +31316,7 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>A2269T,G26144T</t>
+          <t>C8782T,G11083T,T28144C,C29095T</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr"/>
@@ -34121,37 +31324,37 @@
       <c r="AD33" t="inlineStr"/>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>ORF3a:G251V</t>
+          <t>ORF1a:L3606F,ORF8:L84S</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>T14805C</t>
-        </is>
-      </c>
+      <c r="AH33" t="inlineStr"/>
       <c r="AI33" t="inlineStr"/>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>A2269T</t>
+          <t>G11083T,C29095T</t>
         </is>
       </c>
       <c r="AK33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL33" t="n">
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN33" t="n">
         <v>2</v>
       </c>
       <c r="AO33" t="inlineStr"/>
       <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
+      <c r="AQ33" t="inlineStr">
+        <is>
+          <t>ORF1a:L3606F</t>
+        </is>
+      </c>
       <c r="AR33" t="n">
         <v>0</v>
       </c>
@@ -34159,45 +31362,43 @@
         <v>0</v>
       </c>
       <c r="AT33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV33" t="n">
-        <v>11083</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AV33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>A2269T,G26144T</t>
+          <t>G11083T,C29095T</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>ORF3a:G251V</t>
+          <t>ORF1a:L3606F</t>
         </is>
       </c>
       <c r="BA33" t="inlineStr"/>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>A2269T,G26144T</t>
+          <t>G11083T,C29095T</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr"/>
       <c r="BE33" t="inlineStr">
         <is>
-          <t>ORF3a:G251V</t>
+          <t>ORF1a:L3606F</t>
         </is>
       </c>
       <c r="BF33" t="inlineStr"/>
@@ -34211,11 +31412,7 @@
       <c r="BN33" t="inlineStr"/>
       <c r="BO33" t="inlineStr"/>
       <c r="BP33" t="inlineStr"/>
-      <c r="BQ33" t="inlineStr">
-        <is>
-          <t>ORF1a:3606</t>
-        </is>
-      </c>
+      <c r="BQ33" t="inlineStr"/>
       <c r="BR33" t="inlineStr"/>
       <c r="BS33" t="n">
         <v>3000</v>
@@ -34229,7 +31426,7 @@
         </is>
       </c>
       <c r="BV33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BW33" t="n">
         <v>10</v>
@@ -34249,7 +31446,7 @@
         <v>24</v>
       </c>
       <c r="CB33" t="n">
-        <v>-1</v>
+        <v>-6</v>
       </c>
       <c r="CC33" t="n">
         <v>0</v>
@@ -34260,7 +31457,7 @@
         </is>
       </c>
       <c r="CE33" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="CF33" t="inlineStr"/>
       <c r="CG33" t="n">
@@ -34312,11 +31509,11 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MN985325.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA-CDC-02982586-001/2020, complete genome</t>
+          <t>MN938384.1 Severe acute respiratory syndrome coronavirus 2 isolate 2019-nCoV_HKU-SZ-002a_2020, complete genome</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -34384,16 +31581,16 @@
         <v>0</v>
       </c>
       <c r="U34" t="n">
-        <v>89634</v>
+        <v>89502</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="W34" t="n">
-        <v>29882</v>
+        <v>29870</v>
       </c>
       <c r="X34" t="n">
-        <v>0.9992977293248168</v>
+        <v>0.9978263050530048</v>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
@@ -34405,7 +31602,7 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>C8782T,C18060T,T28144C</t>
+          <t>C8782T,T28144C,C29095T</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr"/>
@@ -34422,7 +31619,7 @@
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>C18060T</t>
+          <t>C29095T</t>
         </is>
       </c>
       <c r="AK34" t="n">
@@ -34460,7 +31657,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>C18060T</t>
+          <t>C29095T</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -34473,7 +31670,7 @@
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>C18060T</t>
+          <t>C29095T</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr"/>
@@ -34586,37 +31783,37 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MN938384.1 Severe acute respiratory syndrome coronavirus 2 isolate 2019-nCoV_HKU-SZ-002a_2020, complete genome</t>
+          <t>LC529905.1 Severe acute respiratory syndrome coronavirus 2 TKYE6182_2020 RNA, complete genome</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>19B</t>
+          <t>19A</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -34646,7 +31843,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -34658,16 +31855,16 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>89502</v>
+        <v>89697</v>
       </c>
       <c r="V35" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>29870</v>
+        <v>29903</v>
       </c>
       <c r="X35" t="n">
-        <v>0.9978263050530048</v>
+        <v>1</v>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
@@ -34679,7 +31876,7 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>C8782T,T28144C,C29095T</t>
+          <t>C15324T,C25810G,C29303T</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr"/>
@@ -34687,7 +31884,7 @@
       <c r="AD35" t="inlineStr"/>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>ORF8:L84S</t>
+          <t>N:P344S,ORF3a:L140V</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr"/>
@@ -34696,7 +31893,7 @@
       <c r="AI35" t="inlineStr"/>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>C29095T</t>
+          <t>C15324T,C25810G,C29303T</t>
         </is>
       </c>
       <c r="AK35" t="n">
@@ -34706,14 +31903,18 @@
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AO35" t="inlineStr"/>
       <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
+      <c r="AQ35" t="inlineStr">
+        <is>
+          <t>N:P344S,ORF3a:L140V</t>
+        </is>
+      </c>
       <c r="AR35" t="n">
         <v>0</v>
       </c>
@@ -34721,37 +31922,45 @@
         <v>0</v>
       </c>
       <c r="AT35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AV35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>C29095T</t>
+          <t>C15324T,C25810G,C29303T</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>N:P344S,ORF3a:L140V</t>
+        </is>
+      </c>
       <c r="BA35" t="inlineStr"/>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>internal_b384</t>
+          <t>NODE_0000000</t>
         </is>
       </c>
       <c r="BC35" t="inlineStr">
         <is>
-          <t>C29095T</t>
+          <t>C15324T,C25810G,C29303T</t>
         </is>
       </c>
       <c r="BD35" t="inlineStr"/>
-      <c r="BE35" t="inlineStr"/>
+      <c r="BE35" t="inlineStr">
+        <is>
+          <t>N:P344S,ORF3a:L140V</t>
+        </is>
+      </c>
       <c r="BF35" t="inlineStr"/>
       <c r="BG35" t="inlineStr"/>
       <c r="BH35" t="inlineStr"/>
@@ -34797,7 +32006,7 @@
         <v>24</v>
       </c>
       <c r="CB35" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="CC35" t="n">
         <v>0</v>
@@ -34808,7 +32017,7 @@
         </is>
       </c>
       <c r="CE35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="CF35" t="inlineStr"/>
       <c r="CG35" t="n">
@@ -34860,37 +32069,37 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LC529905.1 Severe acute respiratory syndrome coronavirus 2 TKYE6182_2020 RNA, complete genome</t>
+          <t>MN985325.1 Severe acute respiratory syndrome coronavirus 2 isolate SARS-CoV-2/human/USA/WA-CDC-02982586-001/2020, complete genome</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>19A</t>
+          <t>19B</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -34920,7 +32129,7 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -34932,16 +32141,16 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>89697</v>
+        <v>89634</v>
       </c>
       <c r="V36" t="n">
         <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>29903</v>
+        <v>29882</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0.9992977293248168</v>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
@@ -34953,7 +32162,7 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>C15324T,C25810G,C29303T</t>
+          <t>C8782T,C18060T,T28144C</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr"/>
@@ -34961,7 +32170,7 @@
       <c r="AD36" t="inlineStr"/>
       <c r="AE36" t="inlineStr">
         <is>
-          <t>N:P344S,ORF3a:L140V</t>
+          <t>ORF8:L84S</t>
         </is>
       </c>
       <c r="AF36" t="inlineStr"/>
@@ -34970,7 +32179,7 @@
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>C15324T,C25810G,C29303T</t>
+          <t>C18060T</t>
         </is>
       </c>
       <c r="AK36" t="n">
@@ -34980,18 +32189,14 @@
         <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AN36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AO36" t="inlineStr"/>
       <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr">
-        <is>
-          <t>N:P344S,ORF3a:L140V</t>
-        </is>
-      </c>
+      <c r="AQ36" t="inlineStr"/>
       <c r="AR36" t="n">
         <v>0</v>
       </c>
@@ -34999,45 +32204,37 @@
         <v>0</v>
       </c>
       <c r="AT36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AV36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>C15324T,C25810G,C29303T</t>
+          <t>C18060T</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>N:P344S,ORF3a:L140V</t>
-        </is>
-      </c>
+      <c r="AZ36" t="inlineStr"/>
       <c r="BA36" t="inlineStr"/>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>NODE_0000000</t>
+          <t>internal_b384</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>C15324T,C25810G,C29303T</t>
+          <t>C18060T</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr"/>
-      <c r="BE36" t="inlineStr">
-        <is>
-          <t>N:P344S,ORF3a:L140V</t>
-        </is>
-      </c>
+      <c r="BE36" t="inlineStr"/>
       <c r="BF36" t="inlineStr"/>
       <c r="BG36" t="inlineStr"/>
       <c r="BH36" t="inlineStr"/>
@@ -35083,7 +32280,7 @@
         <v>24</v>
       </c>
       <c r="CB36" t="n">
-        <v>-5</v>
+        <v>-7</v>
       </c>
       <c r="CC36" t="n">
         <v>0</v>
@@ -35094,7 +32291,7 @@
         </is>
       </c>
       <c r="CE36" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="CF36" t="inlineStr"/>
       <c r="CG36" t="n">
